--- a/DATA/穂波線.xlsx
+++ b/DATA/穂波線.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BVE5\honami\DATA\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B64B6431-E963-4038-AF27-122FC575DF67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" activeTab="1" xr2:uid="{AC3BFB01-1044-4FB7-8134-CE4EEBDA8ECC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="停車駅など" sheetId="1" r:id="rId1"/>
@@ -22,7 +16,7 @@
     <sheet name="放送台本" sheetId="9" r:id="rId7"/>
     <sheet name="Excel方眼" sheetId="4" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1377" uniqueCount="732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1378" uniqueCount="735">
   <si>
     <t>穂波線(本線)</t>
     <rPh sb="0" eb="2">
@@ -4174,12 +4168,26 @@
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>₁</t>
+  </si>
+  <si>
+    <t>₁</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>洗1</t>
+    <rPh sb="0" eb="1">
+      <t>アラ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4321,6 +4329,21 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="6"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="19">
     <fill>
@@ -4432,7 +4455,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="34">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -4587,32 +4610,6 @@
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border diagonalDown="1">
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="thin">
-        <color auto="1"/>
-      </diagonal>
-    </border>
-    <border diagonalDown="1">
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal style="thin">
-        <color auto="1"/>
-      </diagonal>
     </border>
     <border>
       <left style="thin">
@@ -4819,7 +4816,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4916,7 +4913,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1">
@@ -4967,14 +4964,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1">
@@ -4987,12 +4990,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -5014,10 +5011,10 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5047,7 +5044,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
@@ -5065,7 +5062,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
@@ -5074,7 +5071,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -5082,12 +5079,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -5099,10 +5090,10 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5162,10 +5153,10 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -5174,6 +5165,19 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5183,7 +5187,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -5195,7 +5199,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -5206,7 +5210,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -5253,7 +5257,7 @@
         <xdr:cNvPr id="3" name="正方形/長方形 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2AA0286A-722C-4B52-9F53-499BEAFC7327}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2AA0286A-722C-4B52-9F53-499BEAFC7327}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5319,7 +5323,7 @@
         <xdr:cNvPr id="31" name="グループ化 30">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{50E70993-A161-6B43-980E-98ABF93F479B}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{50E70993-A161-6B43-980E-98ABF93F479B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5327,8 +5331,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6909265" y="988758"/>
-          <a:ext cx="862336" cy="389008"/>
+          <a:off x="7025941" y="1004851"/>
+          <a:ext cx="874406" cy="393032"/>
           <a:chOff x="6953250" y="994825"/>
           <a:chExt cx="866886" cy="390525"/>
         </a:xfrm>
@@ -5338,7 +5342,7 @@
           <xdr:cNvPr id="2" name="正方形/長方形 1">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CEFFBF47-73FD-33FB-EA47-AE609429D262}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CEFFBF47-73FD-33FB-EA47-AE609429D262}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5389,7 +5393,7 @@
           <xdr:cNvPr id="5" name="直線コネクタ 4">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CCE9F4DA-FDF2-236C-18CD-CEDED501DE65}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CCE9F4DA-FDF2-236C-18CD-CEDED501DE65}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5445,7 +5449,7 @@
         <xdr:cNvPr id="11" name="正方形/長方形 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6A3FE79-E6CA-4242-9AF0-AC089929DEBB}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6A3FE79-E6CA-4242-9AF0-AC089929DEBB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5511,7 +5515,7 @@
         <xdr:cNvPr id="12" name="正方形/長方形 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E1F1A11-A0C6-4C03-A432-CD0C069F9012}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E1F1A11-A0C6-4C03-A432-CD0C069F9012}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5589,7 +5593,7 @@
         <xdr:cNvPr id="13" name="正方形/長方形 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BCE4164B-1EB0-4EC6-B065-60EF1E8CB026}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BCE4164B-1EB0-4EC6-B065-60EF1E8CB026}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5662,7 +5666,7 @@
         <xdr:cNvPr id="14" name="正方形/長方形 13">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D77EA826-615F-4D66-BE07-EA54E6CB44B6}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D77EA826-615F-4D66-BE07-EA54E6CB44B6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5728,7 +5732,7 @@
         <xdr:cNvPr id="15" name="正方形/長方形 14">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8B64431-D41E-4BAF-9852-211A42AD21C0}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8B64431-D41E-4BAF-9852-211A42AD21C0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5794,7 +5798,7 @@
         <xdr:cNvPr id="17" name="直線コネクタ 16">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C43DA58-2B05-D319-DA0E-1E55B44390C0}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C43DA58-2B05-D319-DA0E-1E55B44390C0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5849,7 +5853,7 @@
         <xdr:cNvPr id="19" name="直線コネクタ 18">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE085791-EAB2-40A1-A4DB-B72CF83F28E6}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE085791-EAB2-40A1-A4DB-B72CF83F28E6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5904,7 +5908,7 @@
         <xdr:cNvPr id="22" name="正方形/長方形 21">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D5152BE-C59A-4CBD-8637-E19D249D75F3}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D5152BE-C59A-4CBD-8637-E19D249D75F3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5970,7 +5974,7 @@
         <xdr:cNvPr id="23" name="正方形/長方形 22">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D102B36-F6EE-489B-81BE-E81ADE70DADD}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D102B36-F6EE-489B-81BE-E81ADE70DADD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6036,7 +6040,7 @@
         <xdr:cNvPr id="24" name="正方形/長方形 23">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1C841B9-2CD1-4810-ACF7-8CA98DCEE781}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1C841B9-2CD1-4810-ACF7-8CA98DCEE781}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6102,7 +6106,7 @@
         <xdr:cNvPr id="25" name="正方形/長方形 24">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D70A3514-7400-4381-A929-0EC0A523069D}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D70A3514-7400-4381-A929-0EC0A523069D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6168,7 +6172,7 @@
         <xdr:cNvPr id="26" name="正方形/長方形 25">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{335C0ECF-D028-4349-89B0-A7B9B8082136}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{335C0ECF-D028-4349-89B0-A7B9B8082136}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6234,7 +6238,7 @@
         <xdr:cNvPr id="28" name="直線コネクタ 27">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5E48B68-AA28-71C8-C7EA-96CE376AD5B7}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5E48B68-AA28-71C8-C7EA-96CE376AD5B7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6289,7 +6293,7 @@
         <xdr:cNvPr id="30" name="直線コネクタ 29">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC09CD4F-C280-420E-92A8-DE435DC886A6}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC09CD4F-C280-420E-92A8-DE435DC886A6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6344,7 +6348,7 @@
         <xdr:cNvPr id="32" name="直線コネクタ 31">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BB436BD-845E-49F3-B7D7-C5F8FBE82BA4}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BB436BD-845E-49F3-B7D7-C5F8FBE82BA4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6399,7 +6403,7 @@
         <xdr:cNvPr id="33" name="正方形/長方形 32">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91851EEC-5146-4CDE-B541-7544ECFDE0A3}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91851EEC-5146-4CDE-B541-7544ECFDE0A3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6465,7 +6469,7 @@
         <xdr:cNvPr id="34" name="正方形/長方形 33">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5749ED0B-BD1C-414E-B48D-3357A3FC2750}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5749ED0B-BD1C-414E-B48D-3357A3FC2750}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6531,7 +6535,7 @@
         <xdr:cNvPr id="35" name="正方形/長方形 34">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E1963CB-E6B4-4CAD-A5A8-48456BC94036}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E1963CB-E6B4-4CAD-A5A8-48456BC94036}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6597,7 +6601,7 @@
         <xdr:cNvPr id="36" name="正方形/長方形 35">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1005B239-BD4B-41AF-8287-632BEFCD6B7B}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1005B239-BD4B-41AF-8287-632BEFCD6B7B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6663,7 +6667,7 @@
         <xdr:cNvPr id="37" name="正方形/長方形 36">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{364FA14C-887D-432C-8D4A-1BD61F378AEB}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{364FA14C-887D-432C-8D4A-1BD61F378AEB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6729,7 +6733,7 @@
         <xdr:cNvPr id="38" name="正方形/長方形 37">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5235D326-C9A5-4E15-91A7-9A7EBFA18872}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5235D326-C9A5-4E15-91A7-9A7EBFA18872}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6795,7 +6799,7 @@
         <xdr:cNvPr id="39" name="正方形/長方形 38">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA13864A-A863-4986-9240-456FB70DEB81}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA13864A-A863-4986-9240-456FB70DEB81}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6861,7 +6865,7 @@
         <xdr:cNvPr id="40" name="正方形/長方形 39">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49996F1F-458D-40E1-B2EC-5A46C024BC21}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49996F1F-458D-40E1-B2EC-5A46C024BC21}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6927,7 +6931,7 @@
         <xdr:cNvPr id="41" name="正方形/長方形 40">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4B64AAC-3CD4-455B-88A7-4283B62F3519}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4B64AAC-3CD4-455B-88A7-4283B62F3519}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6993,7 +6997,7 @@
         <xdr:cNvPr id="42" name="正方形/長方形 41">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27883848-66EB-4C47-A9BF-996309B56BA2}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27883848-66EB-4C47-A9BF-996309B56BA2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7059,7 +7063,7 @@
         <xdr:cNvPr id="43" name="正方形/長方形 42">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{570358D7-28B5-4199-8B89-11CDCC1E07F2}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{570358D7-28B5-4199-8B89-11CDCC1E07F2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7125,7 +7129,7 @@
         <xdr:cNvPr id="44" name="正方形/長方形 43">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8A86EEB-FF3C-4529-88EB-DCC85CF973FD}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8A86EEB-FF3C-4529-88EB-DCC85CF973FD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7191,7 +7195,7 @@
         <xdr:cNvPr id="45" name="正方形/長方形 44">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F768BBD-9CF1-449F-97E1-FCF8C255E910}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F768BBD-9CF1-449F-97E1-FCF8C255E910}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7257,7 +7261,7 @@
         <xdr:cNvPr id="46" name="正方形/長方形 45">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9359C628-FC1E-43AB-94E4-ED579A22CC2B}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9359C628-FC1E-43AB-94E4-ED579A22CC2B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7323,7 +7327,7 @@
         <xdr:cNvPr id="47" name="正方形/長方形 46">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D125A3B8-CD02-4C4F-8FA0-2EF2DE580C14}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D125A3B8-CD02-4C4F-8FA0-2EF2DE580C14}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7389,7 +7393,7 @@
         <xdr:cNvPr id="48" name="正方形/長方形 47">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{218EC423-179D-44E6-9946-74A639133131}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{218EC423-179D-44E6-9946-74A639133131}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7455,7 +7459,7 @@
         <xdr:cNvPr id="49" name="正方形/長方形 48">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5ACFDB6B-09A5-47F7-9CD1-AB092B699C7A}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5ACFDB6B-09A5-47F7-9CD1-AB092B699C7A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7521,7 +7525,7 @@
         <xdr:cNvPr id="50" name="正方形/長方形 49">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2AD98D1-FB95-4EFD-8709-B84DC77B7481}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2AD98D1-FB95-4EFD-8709-B84DC77B7481}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7571,13 +7575,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>35</xdr:col>
+      <xdr:col>37</xdr:col>
       <xdr:colOff>54835</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>43451</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>38</xdr:col>
+      <xdr:col>40</xdr:col>
       <xdr:colOff>207235</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>215415</xdr:rowOff>
@@ -7587,7 +7591,7 @@
         <xdr:cNvPr id="51" name="正方形/長方形 50">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AA79B62-0B98-4C45-B626-6F700988BCF4}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AA79B62-0B98-4C45-B626-6F700988BCF4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7637,13 +7641,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>35</xdr:col>
+      <xdr:col>37</xdr:col>
       <xdr:colOff>49942</xdr:colOff>
       <xdr:row>28</xdr:row>
       <xdr:rowOff>34187</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>38</xdr:col>
+      <xdr:col>40</xdr:col>
       <xdr:colOff>202342</xdr:colOff>
       <xdr:row>28</xdr:row>
       <xdr:rowOff>206151</xdr:rowOff>
@@ -7653,7 +7657,7 @@
         <xdr:cNvPr id="52" name="正方形/長方形 51">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{800C0103-1509-4DA7-AC81-89AAC2C75EC3}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{800C0103-1509-4DA7-AC81-89AAC2C75EC3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7703,23 +7707,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>46</xdr:col>
-      <xdr:colOff>43081</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>34855</xdr:rowOff>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>43439</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>34241</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>49</xdr:col>
-      <xdr:colOff>195481</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>206819</xdr:rowOff>
+      <xdr:col>51</xdr:col>
+      <xdr:colOff>195839</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>206205</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="53" name="正方形/長方形 52">
+        <xdr:cNvPr id="54" name="正方形/長方形 53">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C872B6E-FAAD-4023-BCC4-FA34E60E83AA}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E281361C-7F70-49DF-8421-122F1D872524}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7727,7 +7731,205 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5809567" y="6281882"/>
+          <a:off x="11538753" y="6500355"/>
+          <a:ext cx="870857" cy="171964"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>63</xdr:col>
+      <xdr:colOff>38506</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>38007</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>66</xdr:col>
+      <xdr:colOff>190906</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>206828</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="55" name="正方形/長方形 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E671E169-677B-409E-BB85-19B5F3583645}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14886620" y="6504121"/>
+          <a:ext cx="870857" cy="408307"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>63</xdr:col>
+      <xdr:colOff>50470</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>43695</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>66</xdr:col>
+      <xdr:colOff>202870</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>215659</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="56" name="正方形/長方形 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6EA2509F-ECF7-42D2-B1C0-638380A3AAB1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15138070" y="6030838"/>
+          <a:ext cx="870857" cy="171964"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>60</xdr:col>
+      <xdr:colOff>69937</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>32810</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>63</xdr:col>
+      <xdr:colOff>222338</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>204774</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="57" name="正方形/長方形 56">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75CBF8B6-EE9A-41A0-B86A-E22CAA17A0BB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14005613" y="7721459"/>
           <a:ext cx="873211" cy="171964"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7769,23 +7971,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>46</xdr:col>
-      <xdr:colOff>43439</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>39684</xdr:rowOff>
+      <xdr:col>62</xdr:col>
+      <xdr:colOff>50716</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>30751</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>49</xdr:col>
-      <xdr:colOff>195839</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>211648</xdr:rowOff>
+      <xdr:col>65</xdr:col>
+      <xdr:colOff>203116</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>202715</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="54" name="正方形/長方形 53">
+        <xdr:cNvPr id="58" name="正方形/長方形 57">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E281361C-7F70-49DF-8421-122F1D872524}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1CCAC5D-E762-470F-AE78-EF252F98081C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7793,7 +7995,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5809925" y="6767252"/>
+          <a:off x="14466932" y="7238859"/>
           <a:ext cx="873211" cy="171964"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7835,23 +8037,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>60</xdr:col>
+      <xdr:col>37</xdr:col>
       <xdr:colOff>54835</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>43451</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>63</xdr:col>
+      <xdr:col>40</xdr:col>
       <xdr:colOff>207235</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>215415</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="55" name="正方形/長方形 54">
+        <xdr:cNvPr id="59" name="正方形/長方形 58">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E671E169-677B-409E-BB85-19B5F3583645}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D557C5F1-80B1-4855-8DC8-2B1FCA585BC7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7901,277 +8103,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>60</xdr:col>
-      <xdr:colOff>61356</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>32810</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>63</xdr:col>
-      <xdr:colOff>213756</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>204774</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="56" name="正方形/長方形 55">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6EA2509F-ECF7-42D2-B1C0-638380A3AAB1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14237302" y="6760378"/>
-          <a:ext cx="873211" cy="171964"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>58</xdr:col>
-      <xdr:colOff>69937</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>32810</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>61</xdr:col>
-      <xdr:colOff>222338</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>204774</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="57" name="正方形/長方形 56">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75CBF8B6-EE9A-41A0-B86A-E22CAA17A0BB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14005613" y="7721459"/>
-          <a:ext cx="873211" cy="171964"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>60</xdr:col>
-      <xdr:colOff>50716</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>30751</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>63</xdr:col>
-      <xdr:colOff>203116</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>202715</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="58" name="正方形/長方形 57">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1CCAC5D-E762-470F-AE78-EF252F98081C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14466932" y="7238859"/>
-          <a:ext cx="873211" cy="171964"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>54835</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>43451</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>207235</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>215415</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="59" name="正方形/長方形 58">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D557C5F1-80B1-4855-8DC8-2B1FCA585BC7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8464294" y="6290478"/>
-          <a:ext cx="873211" cy="171964"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>35</xdr:col>
+      <xdr:col>37</xdr:col>
       <xdr:colOff>49942</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>34187</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>38</xdr:col>
+      <xdr:col>40</xdr:col>
       <xdr:colOff>202342</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>206151</xdr:rowOff>
@@ -8181,7 +8119,7 @@
         <xdr:cNvPr id="60" name="正方形/長方形 59">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B0BBF34-F5B1-499A-9995-8F1EB0EA70AC}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B0BBF34-F5B1-499A-9995-8F1EB0EA70AC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8231,13 +8169,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>46</xdr:col>
+      <xdr:col>48</xdr:col>
       <xdr:colOff>50716</xdr:colOff>
       <xdr:row>30</xdr:row>
       <xdr:rowOff>39332</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>49</xdr:col>
+      <xdr:col>51</xdr:col>
       <xdr:colOff>203116</xdr:colOff>
       <xdr:row>30</xdr:row>
       <xdr:rowOff>211296</xdr:rowOff>
@@ -8247,7 +8185,7 @@
         <xdr:cNvPr id="61" name="正方形/長方形 60">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1F224E9-FB39-4FFA-A2B0-6BA7D6F4D9D2}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1F224E9-FB39-4FFA-A2B0-6BA7D6F4D9D2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8297,13 +8235,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>46</xdr:col>
+      <xdr:col>48</xdr:col>
       <xdr:colOff>48657</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>37273</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>49</xdr:col>
+      <xdr:col>51</xdr:col>
       <xdr:colOff>201057</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>209237</xdr:rowOff>
@@ -8313,7 +8251,7 @@
         <xdr:cNvPr id="62" name="正方形/長方形 61">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2705E854-BFB9-46CD-8695-F1B9F5F96FA2}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2705E854-BFB9-46CD-8695-F1B9F5F96FA2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8379,7 +8317,7 @@
         <xdr:cNvPr id="4" name="正方形/長方形 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFF8E44F-B380-473B-9A0B-D1274C371D35}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFF8E44F-B380-473B-9A0B-D1274C371D35}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8454,7 +8392,7 @@
         <xdr:cNvPr id="6" name="正方形/長方形 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7CDBEC32-BD8E-405A-A7FD-E9C9340C2C56}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7CDBEC32-BD8E-405A-A7FD-E9C9340C2C56}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8520,7 +8458,7 @@
         <xdr:cNvPr id="7" name="正方形/長方形 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E8334E3-341E-460E-BAB7-F7F7F7E6D053}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E8334E3-341E-460E-BAB7-F7F7F7E6D053}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8586,7 +8524,7 @@
         <xdr:cNvPr id="8" name="正方形/長方形 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D3532C2-A912-4052-815A-E918EC3DA059}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D3532C2-A912-4052-815A-E918EC3DA059}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8652,7 +8590,7 @@
         <xdr:cNvPr id="9" name="直線コネクタ 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE861EC0-1FD7-4679-8981-FD9914BEDC43}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE861EC0-1FD7-4679-8981-FD9914BEDC43}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8707,7 +8645,7 @@
         <xdr:cNvPr id="18" name="直線コネクタ 17">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D9189D1-6F66-43CE-BC98-FAED9C2BA6E9}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D9189D1-6F66-43CE-BC98-FAED9C2BA6E9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8762,7 +8700,7 @@
         <xdr:cNvPr id="27" name="正方形/長方形 26">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F61270D0-833C-4D48-BBB5-0F50624F29D4}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F61270D0-833C-4D48-BBB5-0F50624F29D4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8839,7 +8777,7 @@
         <xdr:cNvPr id="29" name="正方形/長方形 28">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B00F0BD-A420-457A-AA47-5B511B00402E}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B00F0BD-A420-457A-AA47-5B511B00402E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8849,6 +8787,81 @@
         <a:xfrm>
           <a:off x="4296514" y="11102130"/>
           <a:ext cx="212404" cy="171134"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>洗</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>69</xdr:col>
+      <xdr:colOff>68140</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>46158</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>70</xdr:col>
+      <xdr:colOff>1148</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>17478</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="63" name="正方形/長方形 62">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFF8E44F-B380-473B-9A0B-D1274C371D35}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="2717402">
+          <a:off x="16573498" y="6291943"/>
+          <a:ext cx="210805" cy="172494"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8919,7 +8932,7 @@
         <xdr:cNvPr id="5" name="直線コネクタ 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9425106-6FC1-4A83-91D8-47A156D2FCE7}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9425106-6FC1-4A83-91D8-47A156D2FCE7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8974,7 +8987,7 @@
         <xdr:cNvPr id="6" name="正方形/長方形 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC827B9A-3B92-481B-A989-EDBA52D664F6}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC827B9A-3B92-481B-A989-EDBA52D664F6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9040,7 +9053,7 @@
         <xdr:cNvPr id="63" name="グループ化 62">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0ABBA77D-24B8-BE09-348C-F18ECB809347}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0ABBA77D-24B8-BE09-348C-F18ECB809347}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9048,8 +9061,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm rot="16200000">
-          <a:off x="1136162" y="2531587"/>
-          <a:ext cx="866774" cy="171964"/>
+          <a:off x="1152647" y="2570054"/>
+          <a:ext cx="877765" cy="171964"/>
           <a:chOff x="7646381" y="518111"/>
           <a:chExt cx="864337" cy="171964"/>
         </a:xfrm>
@@ -9059,7 +9072,7 @@
           <xdr:cNvPr id="7" name="正方形/長方形 6">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDC15559-E105-4E8A-8373-349D569FA639}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDC15559-E105-4E8A-8373-349D569FA639}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9110,7 +9123,7 @@
           <xdr:cNvPr id="11" name="直線コネクタ 10">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BC91B11-DCDF-45FB-9EE1-4D8E0A4342DE}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BC91B11-DCDF-45FB-9EE1-4D8E0A4342DE}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9166,7 +9179,7 @@
         <xdr:cNvPr id="62" name="グループ化 61">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B96F339E-6B79-1E11-9E3F-DEF46E6F21D9}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B96F339E-6B79-1E11-9E3F-DEF46E6F21D9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9174,8 +9187,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm rot="16200000">
-          <a:off x="1581455" y="2527072"/>
-          <a:ext cx="1381165" cy="171964"/>
+          <a:off x="1605268" y="2565538"/>
+          <a:ext cx="1399482" cy="171964"/>
           <a:chOff x="7378113" y="1225532"/>
           <a:chExt cx="1377101" cy="171964"/>
         </a:xfrm>
@@ -9185,7 +9198,7 @@
           <xdr:cNvPr id="8" name="正方形/長方形 7">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9834197-1625-416F-9ADF-1FC307EF24F3}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9834197-1625-416F-9ADF-1FC307EF24F3}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9236,7 +9249,7 @@
           <xdr:cNvPr id="12" name="直線コネクタ 11">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{83638F85-2B72-4496-BAE6-41A9B10E1769}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{83638F85-2B72-4496-BAE6-41A9B10E1769}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9276,7 +9289,7 @@
           <xdr:cNvPr id="13" name="直線コネクタ 12">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{463F10A4-A90E-41F8-B0D7-F49023A78FFD}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{463F10A4-A90E-41F8-B0D7-F49023A78FFD}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9332,7 +9345,7 @@
         <xdr:cNvPr id="65" name="正方形/長方形 64">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D8FE911-34AA-48E1-9D2A-EC39F1967DFA}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D8FE911-34AA-48E1-9D2A-EC39F1967DFA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9398,7 +9411,7 @@
         <xdr:cNvPr id="66" name="正方形/長方形 65">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{999FD625-3E67-421B-AA5B-294DBD9FA3B4}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{999FD625-3E67-421B-AA5B-294DBD9FA3B4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9464,7 +9477,7 @@
         <xdr:cNvPr id="68" name="直線コネクタ 67">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2A41156-EF4C-4F41-9F71-3988A45B4297}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2A41156-EF4C-4F41-9F71-3988A45B4297}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9519,7 +9532,7 @@
         <xdr:cNvPr id="69" name="正方形/長方形 68">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81CDA289-A170-4831-9A01-0402C908F5E0}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81CDA289-A170-4831-9A01-0402C908F5E0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9585,7 +9598,7 @@
         <xdr:cNvPr id="70" name="正方形/長方形 69">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2092B39-3F94-4174-BD86-0779A08963DF}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2092B39-3F94-4174-BD86-0779A08963DF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9651,7 +9664,7 @@
         <xdr:cNvPr id="71" name="正方形/長方形 70">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E01B8BB-AD33-4850-95F4-FE0DA36FCC2F}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E01B8BB-AD33-4850-95F4-FE0DA36FCC2F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9717,7 +9730,7 @@
         <xdr:cNvPr id="72" name="正方形/長方形 71">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98F54258-3D00-49B5-BDA0-0C9EEB56349F}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98F54258-3D00-49B5-BDA0-0C9EEB56349F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9783,7 +9796,7 @@
         <xdr:cNvPr id="73" name="正方形/長方形 72">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9EC55466-3AF5-46E7-A15D-F2F07E46AE34}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9EC55466-3AF5-46E7-A15D-F2F07E46AE34}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9849,7 +9862,7 @@
         <xdr:cNvPr id="74" name="正方形/長方形 73">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39E5D7D6-AA03-467F-B355-770119000CA6}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39E5D7D6-AA03-467F-B355-770119000CA6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9915,7 +9928,7 @@
         <xdr:cNvPr id="75" name="正方形/長方形 74">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F69B2D13-CEA7-4CF0-AC8D-3E4050A8BD73}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F69B2D13-CEA7-4CF0-AC8D-3E4050A8BD73}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9981,7 +9994,7 @@
         <xdr:cNvPr id="76" name="正方形/長方形 75">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8635D37F-6492-46CD-9C3D-70738A8E4BF0}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8635D37F-6492-46CD-9C3D-70738A8E4BF0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10047,7 +10060,7 @@
         <xdr:cNvPr id="77" name="正方形/長方形 76">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AEECD2EE-D429-44B9-8517-60A3A0002F7C}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AEECD2EE-D429-44B9-8517-60A3A0002F7C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10113,7 +10126,7 @@
         <xdr:cNvPr id="78" name="正方形/長方形 77">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46877CCB-B76F-4054-883C-AC5FBA079A62}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46877CCB-B76F-4054-883C-AC5FBA079A62}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10179,7 +10192,7 @@
         <xdr:cNvPr id="79" name="正方形/長方形 78">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8876CBE0-E02B-4A2C-9CD9-AB864C5E3B53}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8876CBE0-E02B-4A2C-9CD9-AB864C5E3B53}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10245,7 +10258,7 @@
         <xdr:cNvPr id="82" name="正方形/長方形 81">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB7D67BC-2CC6-4E82-80F5-7D9D162639A1}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB7D67BC-2CC6-4E82-80F5-7D9D162639A1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10311,7 +10324,7 @@
         <xdr:cNvPr id="83" name="正方形/長方形 82">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD509B12-431A-442F-80BC-89E6C876EF67}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD509B12-431A-442F-80BC-89E6C876EF67}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10377,7 +10390,7 @@
         <xdr:cNvPr id="84" name="正方形/長方形 83">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76ADE9BA-0202-492C-BDAC-FD4992945182}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76ADE9BA-0202-492C-BDAC-FD4992945182}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10443,7 +10456,7 @@
         <xdr:cNvPr id="85" name="正方形/長方形 84">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A966F48-B643-4E61-A28C-7D4DCF8659BB}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A966F48-B643-4E61-A28C-7D4DCF8659BB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10509,7 +10522,7 @@
         <xdr:cNvPr id="86" name="正方形/長方形 85">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B12AC7F0-4FC5-4898-A90F-707489333EDC}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B12AC7F0-4FC5-4898-A90F-707489333EDC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10575,7 +10588,7 @@
         <xdr:cNvPr id="87" name="正方形/長方形 86">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1B69830-AA1F-42F8-919B-1CD5C42AF6A9}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1B69830-AA1F-42F8-919B-1CD5C42AF6A9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10641,7 +10654,7 @@
         <xdr:cNvPr id="88" name="正方形/長方形 87">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E576F33-AE0D-4041-9D6A-EEA02ED1C5A6}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E576F33-AE0D-4041-9D6A-EEA02ED1C5A6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10707,7 +10720,7 @@
         <xdr:cNvPr id="89" name="正方形/長方形 88">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12DC1F32-325E-4727-8BB7-47DC4C441113}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12DC1F32-325E-4727-8BB7-47DC4C441113}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10773,7 +10786,7 @@
         <xdr:cNvPr id="90" name="正方形/長方形 89">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31675BF2-DC90-4784-9019-2000F83F747C}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31675BF2-DC90-4784-9019-2000F83F747C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10839,7 +10852,7 @@
         <xdr:cNvPr id="91" name="正方形/長方形 90">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E5B0487-C3F4-4200-A3CB-0B20BEF774BD}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E5B0487-C3F4-4200-A3CB-0B20BEF774BD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10905,7 +10918,7 @@
         <xdr:cNvPr id="92" name="正方形/長方形 91">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{604F7F49-D07E-4608-8E1D-06780BCBB06C}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{604F7F49-D07E-4608-8E1D-06780BCBB06C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10971,7 +10984,7 @@
         <xdr:cNvPr id="93" name="正方形/長方形 92">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDCF5392-553C-4B68-A69B-6F48B2855425}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDCF5392-553C-4B68-A69B-6F48B2855425}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11037,7 +11050,7 @@
         <xdr:cNvPr id="94" name="正方形/長方形 93">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC631BCF-10A9-4B43-82C5-F750D5037028}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC631BCF-10A9-4B43-82C5-F750D5037028}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11103,7 +11116,7 @@
         <xdr:cNvPr id="2" name="直線コネクタ 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78C5047F-C43C-4A5E-8A7B-7874BC13004B}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78C5047F-C43C-4A5E-8A7B-7874BC13004B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11158,7 +11171,7 @@
         <xdr:cNvPr id="3" name="直線コネクタ 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E651FC51-9E3B-48D7-A7EA-84203614EE7A}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E651FC51-9E3B-48D7-A7EA-84203614EE7A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11218,7 +11231,7 @@
         <xdr:cNvPr id="6" name="八角形 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37A16AD4-0D1D-84BE-6234-D69519016ECE}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37A16AD4-0D1D-84BE-6234-D69519016ECE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12065,7 +12078,7 @@
         <xdr:cNvPr id="7" name="正方形/長方形 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CC5525A-F801-48F9-AB74-BAF4ED33A84E}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CC5525A-F801-48F9-AB74-BAF4ED33A84E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12131,7 +12144,7 @@
         <xdr:cNvPr id="8" name="正方形/長方形 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4FE5B91-20DF-46FE-AD63-C542AF836938}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4FE5B91-20DF-46FE-AD63-C542AF836938}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12197,7 +12210,7 @@
         <xdr:cNvPr id="11" name="正方形/長方形 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C76FAF67-9811-4320-A494-6C13EF7BDF74}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C76FAF67-9811-4320-A494-6C13EF7BDF74}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12263,7 +12276,7 @@
         <xdr:cNvPr id="12" name="正方形/長方形 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54E56823-FD5A-4E31-AAEE-5128F14F802B}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54E56823-FD5A-4E31-AAEE-5128F14F802B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12329,7 +12342,7 @@
         <xdr:cNvPr id="13" name="正方形/長方形 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75A16AD4-B682-4146-AFA9-B8870819A209}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75A16AD4-B682-4146-AFA9-B8870819A209}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12395,7 +12408,7 @@
         <xdr:cNvPr id="15" name="正方形/長方形 14">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EDB722F9-3D01-4DF2-BEB6-E063EFDC2CFB}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EDB722F9-3D01-4DF2-BEB6-E063EFDC2CFB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12461,7 +12474,7 @@
         <xdr:cNvPr id="16" name="正方形/長方形 15">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26A9A5B5-D19F-4028-B640-9F1060FF5A9B}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26A9A5B5-D19F-4028-B640-9F1060FF5A9B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12527,7 +12540,7 @@
         <xdr:cNvPr id="17" name="正方形/長方形 16">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B862E11C-7D7A-4438-A99C-B413FB8ECDD5}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B862E11C-7D7A-4438-A99C-B413FB8ECDD5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12593,7 +12606,7 @@
         <xdr:cNvPr id="21" name="正方形/長方形 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCEA7B01-8047-4FED-A1D8-20E2139B489C}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCEA7B01-8047-4FED-A1D8-20E2139B489C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12659,7 +12672,7 @@
         <xdr:cNvPr id="24" name="正方形/長方形 23">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{186615A3-888F-4CE3-AFFE-2F7F7D6CA7AC}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{186615A3-888F-4CE3-AFFE-2F7F7D6CA7AC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12725,7 +12738,7 @@
         <xdr:cNvPr id="25" name="正方形/長方形 24">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01B49186-EB3D-4E78-B0BE-95595DDCB37C}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01B49186-EB3D-4E78-B0BE-95595DDCB37C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12791,7 +12804,7 @@
         <xdr:cNvPr id="26" name="正方形/長方形 25">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34C3C622-8EC2-4AF1-B36D-D6CBFF69B908}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34C3C622-8EC2-4AF1-B36D-D6CBFF69B908}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12857,7 +12870,7 @@
         <xdr:cNvPr id="27" name="正方形/長方形 26">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79AE2880-A9EC-47C4-AC9B-86E7163A26C1}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79AE2880-A9EC-47C4-AC9B-86E7163A26C1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12923,7 +12936,7 @@
         <xdr:cNvPr id="28" name="正方形/長方形 27">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{476FFEF4-ECCB-4DDA-A9B1-E81D0AE75E90}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{476FFEF4-ECCB-4DDA-A9B1-E81D0AE75E90}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12989,7 +13002,7 @@
         <xdr:cNvPr id="34" name="正方形/長方形 33">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8978802-5629-4289-BCBE-E4181FE16EBC}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8978802-5629-4289-BCBE-E4181FE16EBC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13055,7 +13068,7 @@
         <xdr:cNvPr id="36" name="グループ化 35">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F1526FF-9806-93DD-C3D9-6F2E3E005262}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F1526FF-9806-93DD-C3D9-6F2E3E005262}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13074,7 +13087,7 @@
           <xdr:cNvPr id="33" name="正方形/長方形 32">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6617303E-3CF8-4F78-BD9C-254577DE26B6}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6617303E-3CF8-4F78-BD9C-254577DE26B6}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -13125,7 +13138,7 @@
           <xdr:cNvPr id="35" name="直線コネクタ 34">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41FFE5FC-6F33-4447-949B-7E6C073ABFDA}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41FFE5FC-6F33-4447-949B-7E6C073ABFDA}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -13209,7 +13222,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -13261,7 +13274,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -13475,14 +13488,14 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73391FEB-8D42-4CF7-9595-254AC7E82CA8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="C2:CL81"/>
   <sheetFormatPr defaultColWidth="3" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -13573,11 +13586,11 @@
         <v>31</v>
       </c>
       <c r="BY3" s="1"/>
-      <c r="BZ3" s="114" t="s">
+      <c r="BZ3" s="112" t="s">
         <v>591</v>
       </c>
       <c r="CA3" s="1"/>
-      <c r="CB3" s="114" t="s">
+      <c r="CB3" s="112" t="s">
         <v>31</v>
       </c>
       <c r="CC3" s="1"/>
@@ -13589,10 +13602,10 @@
         <v>1</v>
       </c>
       <c r="CG3" s="1"/>
-      <c r="CH3" s="114" t="s">
+      <c r="CH3" s="112" t="s">
         <v>30</v>
       </c>
-      <c r="CJ3" s="116" t="s">
+      <c r="CJ3" s="114" t="s">
         <v>626</v>
       </c>
     </row>
@@ -13654,11 +13667,11 @@
         <v>32</v>
       </c>
       <c r="BY4" s="1"/>
-      <c r="BZ4" s="115" t="s">
+      <c r="BZ4" s="113" t="s">
         <v>31</v>
       </c>
       <c r="CA4" s="1"/>
-      <c r="CB4" s="115" t="s">
+      <c r="CB4" s="113" t="s">
         <v>33</v>
       </c>
       <c r="CC4" s="1"/>
@@ -13670,7 +13683,7 @@
         <v>33</v>
       </c>
       <c r="CG4" s="1"/>
-      <c r="CH4" s="117" t="s">
+      <c r="CH4" s="115" t="s">
         <v>636</v>
       </c>
     </row>
@@ -13891,19 +13904,19 @@
       <c r="BV7" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX7" s="110" t="s">
+      <c r="BX7" s="108" t="s">
         <v>35</v>
       </c>
       <c r="BZ7" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="CD7" s="111" t="s">
+      <c r="CD7" s="109" t="s">
         <v>35</v>
       </c>
       <c r="CF7" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="CH7" s="112" t="s">
+      <c r="CH7" s="110" t="s">
         <v>35</v>
       </c>
       <c r="CI7" t="s">
@@ -13934,11 +13947,11 @@
       <c r="AU8" s="8"/>
       <c r="BI8" s="5"/>
       <c r="BV8" s="4"/>
-      <c r="BX8" s="110"/>
+      <c r="BX8" s="108"/>
       <c r="BZ8" s="7"/>
-      <c r="CD8" s="111"/>
+      <c r="CD8" s="109"/>
       <c r="CF8" s="8"/>
-      <c r="CH8" s="112"/>
+      <c r="CH8" s="110"/>
     </row>
     <row r="9" spans="3:90" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" t="s">
@@ -14015,19 +14028,19 @@
       <c r="BV9" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX9" s="110" t="s">
+      <c r="BX9" s="108" t="s">
         <v>35</v>
       </c>
       <c r="BZ9" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="CD9" s="111" t="s">
+      <c r="CD9" s="109" t="s">
         <v>35</v>
       </c>
       <c r="CF9" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="CH9" s="112" t="s">
+      <c r="CH9" s="110" t="s">
         <v>35</v>
       </c>
       <c r="CI9" t="s">
@@ -14058,11 +14071,11 @@
       <c r="AU10" s="8"/>
       <c r="BI10" s="5"/>
       <c r="BV10" s="4"/>
-      <c r="BX10" s="110"/>
+      <c r="BX10" s="108"/>
       <c r="BZ10" s="7"/>
-      <c r="CD10" s="111"/>
+      <c r="CD10" s="109"/>
       <c r="CF10" s="8"/>
-      <c r="CH10" s="112"/>
+      <c r="CH10" s="110"/>
     </row>
     <row r="11" spans="3:90" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C11" t="s">
@@ -14149,13 +14162,13 @@
       <c r="BV11" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX11" s="110"/>
+      <c r="BX11" s="108"/>
       <c r="BZ11" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="CD11" s="111"/>
+      <c r="CD11" s="109"/>
       <c r="CF11" s="8"/>
-      <c r="CH11" s="112"/>
+      <c r="CH11" s="110"/>
       <c r="CI11" t="s">
         <v>593</v>
       </c>
@@ -14184,11 +14197,11 @@
       <c r="AU12" s="8"/>
       <c r="BI12" s="5"/>
       <c r="BV12" s="4"/>
-      <c r="BX12" s="110"/>
+      <c r="BX12" s="108"/>
       <c r="BZ12" s="7"/>
-      <c r="CD12" s="111"/>
+      <c r="CD12" s="109"/>
       <c r="CF12" s="8"/>
-      <c r="CH12" s="112"/>
+      <c r="CH12" s="110"/>
     </row>
     <row r="13" spans="3:90" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C13" t="s">
@@ -14274,7 +14287,7 @@
       <c r="BV13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX13" s="110" t="s">
+      <c r="BX13" s="108" t="s">
         <v>35</v>
       </c>
       <c r="BZ13" s="7" t="s">
@@ -14283,11 +14296,11 @@
       <c r="CB13" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CD13" s="111" t="s">
+      <c r="CD13" s="109" t="s">
         <v>35</v>
       </c>
       <c r="CF13" s="8"/>
-      <c r="CH13" s="112" t="s">
+      <c r="CH13" s="110" t="s">
         <v>35</v>
       </c>
       <c r="CI13" t="s">
@@ -14318,12 +14331,12 @@
       <c r="AU14" s="8"/>
       <c r="BI14" s="5"/>
       <c r="BV14" s="4"/>
-      <c r="BX14" s="110"/>
+      <c r="BX14" s="108"/>
       <c r="BZ14" s="7"/>
       <c r="CB14" s="6"/>
-      <c r="CD14" s="111"/>
+      <c r="CD14" s="109"/>
       <c r="CF14" s="8"/>
-      <c r="CH14" s="112"/>
+      <c r="CH14" s="110"/>
     </row>
     <row r="15" spans="3:90" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C15" t="s">
@@ -14398,18 +14411,18 @@
       <c r="BV15" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX15" s="110" t="s">
+      <c r="BX15" s="108" t="s">
         <v>35</v>
       </c>
       <c r="BZ15" s="7" t="s">
         <v>35</v>
       </c>
       <c r="CB15" s="6"/>
-      <c r="CD15" s="111" t="s">
+      <c r="CD15" s="109" t="s">
         <v>35</v>
       </c>
       <c r="CF15" s="8"/>
-      <c r="CH15" s="112"/>
+      <c r="CH15" s="110"/>
       <c r="CI15" t="s">
         <v>595</v>
       </c>
@@ -14438,12 +14451,12 @@
       <c r="AU16" s="8"/>
       <c r="BI16" s="5"/>
       <c r="BV16" s="4"/>
-      <c r="BX16" s="110"/>
+      <c r="BX16" s="108"/>
       <c r="BZ16" s="7"/>
       <c r="CB16" s="6"/>
-      <c r="CD16" s="111"/>
+      <c r="CD16" s="109"/>
       <c r="CF16" s="8"/>
-      <c r="CH16" s="112"/>
+      <c r="CH16" s="110"/>
     </row>
     <row r="17" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C17" t="s">
@@ -14526,20 +14539,20 @@
       <c r="BV17" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX17" s="110" t="s">
+      <c r="BX17" s="108" t="s">
         <v>35</v>
       </c>
       <c r="BZ17" s="7" t="s">
         <v>35</v>
       </c>
       <c r="CB17" s="6"/>
-      <c r="CD17" s="111" t="s">
+      <c r="CD17" s="109" t="s">
         <v>35</v>
       </c>
       <c r="CF17" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="CH17" s="112"/>
+      <c r="CH17" s="110"/>
       <c r="CI17" t="s">
         <v>596</v>
       </c>
@@ -14568,12 +14581,12 @@
       <c r="AU18" s="8"/>
       <c r="BI18" s="5"/>
       <c r="BV18" s="4"/>
-      <c r="BX18" s="110"/>
+      <c r="BX18" s="108"/>
       <c r="BZ18" s="7"/>
       <c r="CB18" s="6"/>
-      <c r="CD18" s="111"/>
+      <c r="CD18" s="109"/>
       <c r="CF18" s="8"/>
-      <c r="CH18" s="112"/>
+      <c r="CH18" s="110"/>
     </row>
     <row r="19" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C19" t="s">
@@ -14656,12 +14669,12 @@
       <c r="BV19" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX19" s="110"/>
+      <c r="BX19" s="108"/>
       <c r="BZ19" s="7"/>
       <c r="CB19" s="6"/>
-      <c r="CD19" s="111"/>
+      <c r="CD19" s="109"/>
       <c r="CF19" s="8"/>
-      <c r="CH19" s="112"/>
+      <c r="CH19" s="110"/>
       <c r="CI19" t="s">
         <v>597</v>
       </c>
@@ -14690,12 +14703,12 @@
       <c r="AU20" s="8"/>
       <c r="BI20" s="5"/>
       <c r="BV20" s="4"/>
-      <c r="BX20" s="110"/>
+      <c r="BX20" s="108"/>
       <c r="BZ20" s="7"/>
       <c r="CB20" s="6"/>
-      <c r="CD20" s="111"/>
+      <c r="CD20" s="109"/>
       <c r="CF20" s="8"/>
-      <c r="CH20" s="112"/>
+      <c r="CH20" s="110"/>
     </row>
     <row r="21" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C21" t="s">
@@ -14776,7 +14789,7 @@
       <c r="BV21" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX21" s="110" t="s">
+      <c r="BX21" s="108" t="s">
         <v>35</v>
       </c>
       <c r="BZ21" s="7" t="s">
@@ -14785,9 +14798,9 @@
       <c r="CB21" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CD21" s="111"/>
+      <c r="CD21" s="109"/>
       <c r="CF21" s="8"/>
-      <c r="CH21" s="112"/>
+      <c r="CH21" s="110"/>
       <c r="CI21" t="s">
         <v>598</v>
       </c>
@@ -14816,12 +14829,12 @@
       <c r="AU22" s="8"/>
       <c r="BI22" s="5"/>
       <c r="BV22" s="4"/>
-      <c r="BX22" s="110"/>
+      <c r="BX22" s="108"/>
       <c r="BZ22" s="7"/>
       <c r="CB22" s="6"/>
-      <c r="CD22" s="111"/>
+      <c r="CD22" s="109"/>
       <c r="CF22" s="8"/>
-      <c r="CH22" s="112"/>
+      <c r="CH22" s="110"/>
     </row>
     <row r="23" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C23" t="s">
@@ -14906,12 +14919,12 @@
       <c r="BV23" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX23" s="110"/>
+      <c r="BX23" s="108"/>
       <c r="BZ23" s="7"/>
       <c r="CB23" s="6"/>
-      <c r="CD23" s="111"/>
+      <c r="CD23" s="109"/>
       <c r="CF23" s="8"/>
-      <c r="CH23" s="112"/>
+      <c r="CH23" s="110"/>
       <c r="CI23" t="s">
         <v>599</v>
       </c>
@@ -14940,12 +14953,12 @@
       <c r="AU24" s="8"/>
       <c r="BI24" s="5"/>
       <c r="BV24" s="4"/>
-      <c r="BX24" s="110"/>
+      <c r="BX24" s="108"/>
       <c r="BZ24" s="7"/>
       <c r="CB24" s="6"/>
-      <c r="CD24" s="111"/>
+      <c r="CD24" s="109"/>
       <c r="CF24" s="8"/>
-      <c r="CH24" s="112"/>
+      <c r="CH24" s="110"/>
     </row>
     <row r="25" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C25" t="s">
@@ -15020,16 +15033,16 @@
       <c r="BV25" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX25" s="110" t="s">
+      <c r="BX25" s="108" t="s">
         <v>35</v>
       </c>
       <c r="BZ25" s="7"/>
       <c r="CB25" s="6"/>
-      <c r="CD25" s="111" t="s">
+      <c r="CD25" s="109" t="s">
         <v>35</v>
       </c>
       <c r="CF25" s="8"/>
-      <c r="CH25" s="112"/>
+      <c r="CH25" s="110"/>
       <c r="CI25" t="s">
         <v>600</v>
       </c>
@@ -15058,12 +15071,12 @@
       <c r="AU26" s="8"/>
       <c r="BI26" s="5"/>
       <c r="BV26" s="4"/>
-      <c r="BX26" s="110"/>
+      <c r="BX26" s="108"/>
       <c r="BZ26" s="7"/>
       <c r="CB26" s="6"/>
-      <c r="CD26" s="111"/>
+      <c r="CD26" s="109"/>
       <c r="CF26" s="8"/>
-      <c r="CH26" s="112"/>
+      <c r="CH26" s="110"/>
     </row>
     <row r="27" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C27" t="s">
@@ -15150,12 +15163,12 @@
       <c r="BV27" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX27" s="110"/>
+      <c r="BX27" s="108"/>
       <c r="BZ27" s="7"/>
       <c r="CB27" s="6"/>
-      <c r="CD27" s="111"/>
+      <c r="CD27" s="109"/>
       <c r="CF27" s="8"/>
-      <c r="CH27" s="112"/>
+      <c r="CH27" s="110"/>
       <c r="CI27" t="s">
         <v>601</v>
       </c>
@@ -15177,12 +15190,12 @@
       <c r="AU28" s="8"/>
       <c r="BI28" s="5"/>
       <c r="BV28" s="4"/>
-      <c r="BX28" s="110"/>
+      <c r="BX28" s="108"/>
       <c r="BZ28" s="7"/>
       <c r="CB28" s="6"/>
-      <c r="CD28" s="111"/>
+      <c r="CD28" s="109"/>
       <c r="CF28" s="8"/>
-      <c r="CH28" s="112"/>
+      <c r="CH28" s="110"/>
     </row>
     <row r="29" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C29" t="s">
@@ -15240,14 +15253,14 @@
       <c r="BV29" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX29" s="110" t="s">
+      <c r="BX29" s="108" t="s">
         <v>35</v>
       </c>
       <c r="BZ29" s="7"/>
       <c r="CB29" s="6"/>
-      <c r="CD29" s="111"/>
+      <c r="CD29" s="109"/>
       <c r="CF29" s="8"/>
-      <c r="CH29" s="112"/>
+      <c r="CH29" s="110"/>
       <c r="CI29" t="s">
         <v>602</v>
       </c>
@@ -15261,12 +15274,12 @@
       <c r="J30" s="5"/>
       <c r="K30" s="8"/>
       <c r="BV30" s="4"/>
-      <c r="BX30" s="110"/>
+      <c r="BX30" s="108"/>
       <c r="BZ30" s="7"/>
       <c r="CB30" s="6"/>
-      <c r="CD30" s="111"/>
+      <c r="CD30" s="109"/>
       <c r="CF30" s="8"/>
-      <c r="CH30" s="112"/>
+      <c r="CH30" s="110"/>
     </row>
     <row r="31" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C31" t="s">
@@ -15300,7 +15313,7 @@
       <c r="BV31" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX31" s="110" t="s">
+      <c r="BX31" s="108" t="s">
         <v>35</v>
       </c>
       <c r="BZ31" s="7" t="s">
@@ -15309,9 +15322,9 @@
       <c r="CB31" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CD31" s="111"/>
+      <c r="CD31" s="109"/>
       <c r="CF31" s="8"/>
-      <c r="CH31" s="112"/>
+      <c r="CH31" s="110"/>
       <c r="CI31" t="s">
         <v>603</v>
       </c>
@@ -15325,12 +15338,12 @@
       <c r="J32" s="5"/>
       <c r="K32" s="8"/>
       <c r="BV32" s="4"/>
-      <c r="BX32" s="110"/>
+      <c r="BX32" s="108"/>
       <c r="BZ32" s="7"/>
       <c r="CB32" s="6"/>
-      <c r="CD32" s="111"/>
+      <c r="CD32" s="109"/>
       <c r="CF32" s="8"/>
-      <c r="CH32" s="112"/>
+      <c r="CH32" s="110"/>
     </row>
     <row r="33" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C33" t="s">
@@ -15366,7 +15379,7 @@
       <c r="BV33" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX33" s="110" t="s">
+      <c r="BX33" s="108" t="s">
         <v>35</v>
       </c>
       <c r="BZ33" s="7" t="s">
@@ -15375,13 +15388,13 @@
       <c r="CB33" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CD33" s="111" t="s">
+      <c r="CD33" s="109" t="s">
         <v>35</v>
       </c>
       <c r="CF33" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="CH33" s="112" t="s">
+      <c r="CH33" s="110" t="s">
         <v>35</v>
       </c>
       <c r="CI33" t="s">
@@ -15397,12 +15410,12 @@
       <c r="J34" s="5"/>
       <c r="K34" s="8"/>
       <c r="BV34" s="4"/>
-      <c r="BX34" s="110"/>
+      <c r="BX34" s="108"/>
       <c r="BZ34" s="7"/>
       <c r="CB34" s="6"/>
-      <c r="CD34" s="111"/>
+      <c r="CD34" s="109"/>
       <c r="CF34" s="8"/>
-      <c r="CH34" s="112"/>
+      <c r="CH34" s="110"/>
     </row>
     <row r="35" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C35" t="s">
@@ -15434,16 +15447,16 @@
       <c r="BV35" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX35" s="110"/>
+      <c r="BX35" s="108"/>
       <c r="BZ35" s="7" t="s">
         <v>35</v>
       </c>
       <c r="CB35" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CD35" s="111"/>
+      <c r="CD35" s="109"/>
       <c r="CF35" s="8"/>
-      <c r="CH35" s="113" t="s">
+      <c r="CH35" s="111" t="s">
         <v>36</v>
       </c>
       <c r="CI35" t="s">
@@ -15459,12 +15472,12 @@
       <c r="J36" s="5"/>
       <c r="K36" s="8"/>
       <c r="BV36" s="4"/>
-      <c r="BX36" s="110"/>
+      <c r="BX36" s="108"/>
       <c r="BZ36" s="7"/>
       <c r="CB36" s="6"/>
-      <c r="CD36" s="111"/>
+      <c r="CD36" s="109"/>
       <c r="CF36" s="8"/>
-      <c r="CH36" s="112"/>
+      <c r="CH36" s="110"/>
     </row>
     <row r="37" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C37" t="s">
@@ -15551,7 +15564,7 @@
       <c r="BV37" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX37" s="110" t="s">
+      <c r="BX37" s="108" t="s">
         <v>35</v>
       </c>
       <c r="BZ37" s="7" t="s">
@@ -15560,13 +15573,13 @@
       <c r="CB37" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CD37" s="111" t="s">
+      <c r="CD37" s="109" t="s">
         <v>35</v>
       </c>
       <c r="CF37" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="CH37" s="112" t="s">
+      <c r="CH37" s="110" t="s">
         <v>35</v>
       </c>
       <c r="CI37" t="s">
@@ -15575,12 +15588,12 @@
     </row>
     <row r="38" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="BV38" s="4"/>
-      <c r="BX38" s="110"/>
+      <c r="BX38" s="108"/>
       <c r="BZ38" s="7"/>
       <c r="CB38" s="6"/>
-      <c r="CD38" s="111"/>
+      <c r="CD38" s="109"/>
       <c r="CF38" s="8"/>
-      <c r="CH38" s="112"/>
+      <c r="CH38" s="110"/>
     </row>
     <row r="39" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="H39" s="1" t="s">
@@ -15592,12 +15605,12 @@
       <c r="BV39" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX39" s="110"/>
+      <c r="BX39" s="108"/>
       <c r="BZ39" s="7"/>
       <c r="CB39" s="6"/>
-      <c r="CD39" s="111"/>
+      <c r="CD39" s="109"/>
       <c r="CF39" s="8"/>
-      <c r="CH39" s="112"/>
+      <c r="CH39" s="110"/>
       <c r="CI39" t="s">
         <v>604</v>
       </c>
@@ -15607,12 +15620,12 @@
         <v>166</v>
       </c>
       <c r="BV40" s="4"/>
-      <c r="BX40" s="110"/>
+      <c r="BX40" s="108"/>
       <c r="BZ40" s="7"/>
       <c r="CB40" s="6"/>
-      <c r="CD40" s="111"/>
+      <c r="CD40" s="109"/>
       <c r="CF40" s="8"/>
-      <c r="CH40" s="112"/>
+      <c r="CH40" s="110"/>
     </row>
     <row r="41" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="BS41" t="s">
@@ -15621,7 +15634,7 @@
       <c r="BV41" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX41" s="110" t="s">
+      <c r="BX41" s="108" t="s">
         <v>35</v>
       </c>
       <c r="BZ41" s="7" t="s">
@@ -15630,23 +15643,23 @@
       <c r="CB41" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CD41" s="111" t="s">
+      <c r="CD41" s="109" t="s">
         <v>35</v>
       </c>
       <c r="CF41" s="8"/>
-      <c r="CH41" s="112"/>
+      <c r="CH41" s="110"/>
       <c r="CI41" t="s">
         <v>605</v>
       </c>
     </row>
     <row r="42" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="BV42" s="4"/>
-      <c r="BX42" s="110"/>
+      <c r="BX42" s="108"/>
       <c r="BZ42" s="7"/>
       <c r="CB42" s="6"/>
-      <c r="CD42" s="111"/>
+      <c r="CD42" s="109"/>
       <c r="CF42" s="8"/>
-      <c r="CH42" s="112"/>
+      <c r="CH42" s="110"/>
     </row>
     <row r="43" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C43" t="s">
@@ -15661,67 +15674,67 @@
       <c r="BV43" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX43" s="110" t="s">
+      <c r="BX43" s="108" t="s">
         <v>35</v>
       </c>
       <c r="BZ43" s="7"/>
       <c r="CB43" s="6"/>
-      <c r="CD43" s="111"/>
+      <c r="CD43" s="109"/>
       <c r="CF43" s="8"/>
-      <c r="CH43" s="112"/>
+      <c r="CH43" s="110"/>
       <c r="CI43" t="s">
         <v>606</v>
       </c>
     </row>
     <row r="44" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C44" s="122">
+      <c r="C44" s="125">
         <v>0</v>
       </c>
-      <c r="D44" s="122"/>
+      <c r="D44" s="125"/>
       <c r="E44" t="s">
         <v>688</v>
       </c>
-      <c r="H44" s="122">
+      <c r="H44" s="125">
         <v>100</v>
       </c>
-      <c r="I44" s="122"/>
+      <c r="I44" s="125"/>
       <c r="J44" t="s">
         <v>688</v>
       </c>
-      <c r="M44" s="122">
+      <c r="M44" s="125">
         <v>205</v>
       </c>
-      <c r="N44" s="122"/>
+      <c r="N44" s="125"/>
       <c r="O44" t="s">
         <v>4</v>
       </c>
       <c r="BV44" s="4"/>
-      <c r="BX44" s="110"/>
+      <c r="BX44" s="108"/>
       <c r="BZ44" s="7"/>
       <c r="CB44" s="6"/>
-      <c r="CD44" s="111"/>
+      <c r="CD44" s="109"/>
       <c r="CF44" s="8"/>
-      <c r="CH44" s="112"/>
+      <c r="CH44" s="110"/>
     </row>
     <row r="45" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C45" s="122">
+      <c r="C45" s="125">
         <v>1</v>
       </c>
-      <c r="D45" s="122"/>
+      <c r="D45" s="125"/>
       <c r="E45" t="s">
         <v>689</v>
       </c>
-      <c r="H45" s="122">
+      <c r="H45" s="125">
         <v>101</v>
       </c>
-      <c r="I45" s="122"/>
+      <c r="I45" s="125"/>
       <c r="J45" t="s">
         <v>689</v>
       </c>
-      <c r="M45" s="122">
+      <c r="M45" s="125">
         <v>206</v>
       </c>
-      <c r="N45" s="122"/>
+      <c r="N45" s="125"/>
       <c r="O45" t="s">
         <v>700</v>
       </c>
@@ -15731,73 +15744,73 @@
       <c r="BV45" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX45" s="110" t="s">
+      <c r="BX45" s="108" t="s">
         <v>35</v>
       </c>
       <c r="BZ45" s="7" t="s">
         <v>35</v>
       </c>
       <c r="CB45" s="6"/>
-      <c r="CD45" s="111" t="s">
+      <c r="CD45" s="109" t="s">
         <v>35</v>
       </c>
       <c r="CF45" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="CH45" s="112"/>
+      <c r="CH45" s="110"/>
       <c r="CI45" t="s">
         <v>607</v>
       </c>
     </row>
     <row r="46" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C46" s="122">
+      <c r="C46" s="125">
         <v>2</v>
       </c>
-      <c r="D46" s="122"/>
+      <c r="D46" s="125"/>
       <c r="E46" t="s">
         <v>709</v>
       </c>
-      <c r="H46" s="122">
+      <c r="H46" s="125">
         <v>102</v>
       </c>
-      <c r="I46" s="122"/>
+      <c r="I46" s="125"/>
       <c r="J46" t="s">
         <v>427</v>
       </c>
-      <c r="M46" s="122">
+      <c r="M46" s="125">
         <v>207</v>
       </c>
-      <c r="N46" s="122"/>
+      <c r="N46" s="125"/>
       <c r="O46" t="s">
         <v>61</v>
       </c>
       <c r="BV46" s="4"/>
-      <c r="BX46" s="110"/>
+      <c r="BX46" s="108"/>
       <c r="BZ46" s="7"/>
       <c r="CB46" s="6"/>
-      <c r="CD46" s="111"/>
+      <c r="CD46" s="109"/>
       <c r="CF46" s="8"/>
-      <c r="CH46" s="112"/>
+      <c r="CH46" s="110"/>
     </row>
     <row r="47" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C47" s="122">
+      <c r="C47" s="125">
         <v>3</v>
       </c>
-      <c r="D47" s="122"/>
+      <c r="D47" s="125"/>
       <c r="E47" t="s">
         <v>710</v>
       </c>
-      <c r="H47" s="122">
+      <c r="H47" s="125">
         <v>103</v>
       </c>
-      <c r="I47" s="122"/>
+      <c r="I47" s="125"/>
       <c r="J47" t="s">
         <v>696</v>
       </c>
-      <c r="M47" s="122">
+      <c r="M47" s="125">
         <v>208</v>
       </c>
-      <c r="N47" s="122"/>
+      <c r="N47" s="125"/>
       <c r="O47" t="s">
         <v>62</v>
       </c>
@@ -15807,7 +15820,7 @@
       <c r="BV47" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX47" s="110" t="s">
+      <c r="BX47" s="108" t="s">
         <v>35</v>
       </c>
       <c r="BZ47" s="7" t="s">
@@ -15816,64 +15829,64 @@
       <c r="CB47" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CD47" s="111"/>
+      <c r="CD47" s="109"/>
       <c r="CF47" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="CH47" s="112"/>
+      <c r="CH47" s="110"/>
       <c r="CI47" t="s">
         <v>608</v>
       </c>
     </row>
     <row r="48" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C48" s="122">
+      <c r="C48" s="125">
         <v>4</v>
       </c>
-      <c r="D48" s="122"/>
+      <c r="D48" s="125"/>
       <c r="E48" t="s">
         <v>3</v>
       </c>
-      <c r="H48" s="122">
+      <c r="H48" s="125">
         <v>104</v>
       </c>
-      <c r="I48" s="122"/>
+      <c r="I48" s="125"/>
       <c r="J48" t="s">
         <v>424</v>
       </c>
-      <c r="M48" s="122">
+      <c r="M48" s="125">
         <v>209</v>
       </c>
-      <c r="N48" s="122"/>
+      <c r="N48" s="125"/>
       <c r="O48" t="s">
         <v>701</v>
       </c>
       <c r="BV48" s="4"/>
-      <c r="BX48" s="110"/>
+      <c r="BX48" s="108"/>
       <c r="BZ48" s="7"/>
       <c r="CB48" s="6"/>
-      <c r="CD48" s="111"/>
+      <c r="CD48" s="109"/>
       <c r="CF48" s="8"/>
-      <c r="CH48" s="112"/>
+      <c r="CH48" s="110"/>
     </row>
     <row r="49" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C49" s="122">
+      <c r="C49" s="125">
         <v>5</v>
       </c>
-      <c r="D49" s="122"/>
+      <c r="D49" s="125"/>
       <c r="E49" t="s">
         <v>4</v>
       </c>
-      <c r="H49" s="122">
+      <c r="H49" s="125">
         <v>105</v>
       </c>
-      <c r="I49" s="122"/>
+      <c r="I49" s="125"/>
       <c r="J49" t="s">
         <v>51</v>
       </c>
-      <c r="M49" s="122">
+      <c r="M49" s="125">
         <v>210</v>
       </c>
-      <c r="N49" s="122"/>
+      <c r="N49" s="125"/>
       <c r="O49" t="s">
         <v>64</v>
       </c>
@@ -15883,67 +15896,67 @@
       <c r="BV49" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX49" s="110" t="s">
+      <c r="BX49" s="108" t="s">
         <v>35</v>
       </c>
       <c r="BZ49" s="7"/>
       <c r="CB49" s="6"/>
-      <c r="CD49" s="111"/>
+      <c r="CD49" s="109"/>
       <c r="CF49" s="8"/>
-      <c r="CH49" s="112"/>
+      <c r="CH49" s="110"/>
       <c r="CI49" t="s">
         <v>609</v>
       </c>
     </row>
     <row r="50" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C50" s="122">
+      <c r="C50" s="125">
         <v>6</v>
       </c>
-      <c r="D50" s="122"/>
+      <c r="D50" s="125"/>
       <c r="E50" t="s">
         <v>177</v>
       </c>
-      <c r="H50" s="122">
+      <c r="H50" s="125">
         <v>106</v>
       </c>
-      <c r="I50" s="122"/>
+      <c r="I50" s="125"/>
       <c r="J50" t="s">
         <v>44</v>
       </c>
-      <c r="M50" s="122">
+      <c r="M50" s="125">
         <v>211</v>
       </c>
-      <c r="N50" s="122"/>
+      <c r="N50" s="125"/>
       <c r="O50" t="s">
         <v>65</v>
       </c>
       <c r="BV50" s="4"/>
-      <c r="BX50" s="110"/>
+      <c r="BX50" s="108"/>
       <c r="BZ50" s="7"/>
       <c r="CB50" s="6"/>
-      <c r="CD50" s="111"/>
+      <c r="CD50" s="109"/>
       <c r="CF50" s="8"/>
-      <c r="CH50" s="112"/>
+      <c r="CH50" s="110"/>
     </row>
     <row r="51" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C51" s="122">
+      <c r="C51" s="125">
         <v>7</v>
       </c>
-      <c r="D51" s="122"/>
+      <c r="D51" s="125"/>
       <c r="E51" t="s">
         <v>6</v>
       </c>
-      <c r="H51" s="122">
+      <c r="H51" s="125">
         <v>107</v>
       </c>
-      <c r="I51" s="122"/>
+      <c r="I51" s="125"/>
       <c r="J51" t="s">
         <v>697</v>
       </c>
-      <c r="M51" s="122">
+      <c r="M51" s="125">
         <v>212</v>
       </c>
-      <c r="N51" s="122"/>
+      <c r="N51" s="125"/>
       <c r="O51" t="s">
         <v>66</v>
       </c>
@@ -15953,69 +15966,69 @@
       <c r="BV51" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX51" s="110" t="s">
+      <c r="BX51" s="108" t="s">
         <v>35</v>
       </c>
       <c r="BZ51" s="7" t="s">
         <v>35</v>
       </c>
       <c r="CB51" s="6"/>
-      <c r="CD51" s="111"/>
+      <c r="CD51" s="109"/>
       <c r="CF51" s="8"/>
-      <c r="CH51" s="112"/>
+      <c r="CH51" s="110"/>
       <c r="CI51" t="s">
         <v>610</v>
       </c>
     </row>
     <row r="52" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C52" s="122">
+      <c r="C52" s="125">
         <v>8</v>
       </c>
-      <c r="D52" s="122"/>
+      <c r="D52" s="125"/>
       <c r="E52" t="s">
         <v>672</v>
       </c>
-      <c r="H52" s="122">
+      <c r="H52" s="125">
         <v>108</v>
       </c>
-      <c r="I52" s="122"/>
+      <c r="I52" s="125"/>
       <c r="J52" t="s">
         <v>420</v>
       </c>
-      <c r="M52" s="122">
+      <c r="M52" s="125">
         <v>213</v>
       </c>
-      <c r="N52" s="122"/>
+      <c r="N52" s="125"/>
       <c r="O52" t="s">
         <v>67</v>
       </c>
       <c r="BV52" s="4"/>
-      <c r="BX52" s="110"/>
+      <c r="BX52" s="108"/>
       <c r="BZ52" s="7"/>
       <c r="CB52" s="6"/>
-      <c r="CD52" s="111"/>
+      <c r="CD52" s="109"/>
       <c r="CF52" s="8"/>
-      <c r="CH52" s="112"/>
+      <c r="CH52" s="110"/>
     </row>
     <row r="53" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C53" s="122">
+      <c r="C53" s="125">
         <v>9</v>
       </c>
-      <c r="D53" s="122"/>
+      <c r="D53" s="125"/>
       <c r="E53" t="s">
         <v>690</v>
       </c>
-      <c r="H53" s="122">
+      <c r="H53" s="125">
         <v>109</v>
       </c>
-      <c r="I53" s="122"/>
+      <c r="I53" s="125"/>
       <c r="J53" t="s">
         <v>698</v>
       </c>
-      <c r="M53" s="122">
+      <c r="M53" s="125">
         <v>214</v>
       </c>
-      <c r="N53" s="122"/>
+      <c r="N53" s="125"/>
       <c r="O53" t="s">
         <v>118</v>
       </c>
@@ -16025,69 +16038,69 @@
       <c r="BV53" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX53" s="110" t="s">
+      <c r="BX53" s="108" t="s">
         <v>35</v>
       </c>
       <c r="BZ53" s="7"/>
       <c r="CB53" s="6"/>
-      <c r="CD53" s="111" t="s">
+      <c r="CD53" s="109" t="s">
         <v>35</v>
       </c>
       <c r="CF53" s="8"/>
-      <c r="CH53" s="112"/>
+      <c r="CH53" s="110"/>
       <c r="CI53" t="s">
         <v>611</v>
       </c>
     </row>
     <row r="54" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C54" s="122">
+      <c r="C54" s="125">
         <v>10</v>
       </c>
-      <c r="D54" s="122"/>
+      <c r="D54" s="125"/>
       <c r="E54" t="s">
         <v>13</v>
       </c>
-      <c r="H54" s="122">
+      <c r="H54" s="125">
         <v>110</v>
       </c>
-      <c r="I54" s="122"/>
+      <c r="I54" s="125"/>
       <c r="J54" t="s">
         <v>40</v>
       </c>
-      <c r="M54" s="122">
+      <c r="M54" s="125">
         <v>215</v>
       </c>
-      <c r="N54" s="122"/>
+      <c r="N54" s="125"/>
       <c r="O54" t="s">
         <v>68</v>
       </c>
       <c r="BV54" s="4"/>
-      <c r="BX54" s="110"/>
+      <c r="BX54" s="108"/>
       <c r="BZ54" s="7"/>
       <c r="CB54" s="6"/>
-      <c r="CD54" s="111"/>
+      <c r="CD54" s="109"/>
       <c r="CF54" s="8"/>
-      <c r="CH54" s="112"/>
+      <c r="CH54" s="110"/>
     </row>
     <row r="55" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C55" s="122">
+      <c r="C55" s="125">
         <v>11</v>
       </c>
-      <c r="D55" s="122"/>
+      <c r="D55" s="125"/>
       <c r="E55" t="s">
         <v>694</v>
       </c>
-      <c r="H55" s="122">
+      <c r="H55" s="125">
         <v>111</v>
       </c>
-      <c r="I55" s="122"/>
+      <c r="I55" s="125"/>
       <c r="J55" t="s">
         <v>416</v>
       </c>
-      <c r="M55" s="122">
+      <c r="M55" s="125">
         <v>216</v>
       </c>
-      <c r="N55" s="122"/>
+      <c r="N55" s="125"/>
       <c r="O55" t="s">
         <v>69</v>
       </c>
@@ -16097,67 +16110,67 @@
       <c r="BV55" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX55" s="110" t="s">
+      <c r="BX55" s="108" t="s">
         <v>35</v>
       </c>
       <c r="BZ55" s="7"/>
       <c r="CB55" s="6"/>
-      <c r="CD55" s="111"/>
+      <c r="CD55" s="109"/>
       <c r="CF55" s="8"/>
-      <c r="CH55" s="112"/>
+      <c r="CH55" s="110"/>
       <c r="CI55" t="s">
         <v>612</v>
       </c>
     </row>
     <row r="56" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C56" s="122">
+      <c r="C56" s="125">
         <v>12</v>
       </c>
-      <c r="D56" s="122"/>
+      <c r="D56" s="125"/>
       <c r="E56" t="s">
         <v>691</v>
       </c>
-      <c r="H56" s="122">
+      <c r="H56" s="125">
         <v>112</v>
       </c>
-      <c r="I56" s="122"/>
+      <c r="I56" s="125"/>
       <c r="J56" t="s">
         <v>699</v>
       </c>
-      <c r="M56" s="122">
+      <c r="M56" s="125">
         <v>217</v>
       </c>
-      <c r="N56" s="122"/>
+      <c r="N56" s="125"/>
       <c r="O56" t="s">
         <v>702</v>
       </c>
       <c r="BV56" s="4"/>
-      <c r="BX56" s="110"/>
+      <c r="BX56" s="108"/>
       <c r="BZ56" s="7"/>
       <c r="CB56" s="6"/>
-      <c r="CD56" s="111"/>
+      <c r="CD56" s="109"/>
       <c r="CF56" s="8"/>
-      <c r="CH56" s="112"/>
+      <c r="CH56" s="110"/>
     </row>
     <row r="57" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C57" s="122">
+      <c r="C57" s="125">
         <v>13</v>
       </c>
-      <c r="D57" s="122"/>
+      <c r="D57" s="125"/>
       <c r="E57" t="s">
         <v>17</v>
       </c>
-      <c r="H57" s="122">
+      <c r="H57" s="125">
         <v>113</v>
       </c>
-      <c r="I57" s="122"/>
+      <c r="I57" s="125"/>
       <c r="J57" t="s">
         <v>38</v>
       </c>
-      <c r="M57" s="122">
+      <c r="M57" s="125">
         <v>218</v>
       </c>
-      <c r="N57" s="122"/>
+      <c r="N57" s="125"/>
       <c r="O57" t="s">
         <v>639</v>
       </c>
@@ -16167,37 +16180,37 @@
       <c r="BV57" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX57" s="110"/>
+      <c r="BX57" s="108"/>
       <c r="BZ57" s="7"/>
       <c r="CB57" s="6"/>
-      <c r="CD57" s="111"/>
+      <c r="CD57" s="109"/>
       <c r="CF57" s="8"/>
-      <c r="CH57" s="112"/>
+      <c r="CH57" s="110"/>
       <c r="CI57" t="s">
         <v>613</v>
       </c>
     </row>
     <row r="58" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C58" s="122">
+      <c r="C58" s="125">
         <v>14</v>
       </c>
-      <c r="D58" s="122"/>
+      <c r="D58" s="125"/>
       <c r="E58" t="s">
         <v>692</v>
       </c>
       <c r="BV58" s="4"/>
-      <c r="BX58" s="110"/>
+      <c r="BX58" s="108"/>
       <c r="BZ58" s="7"/>
       <c r="CB58" s="6"/>
-      <c r="CD58" s="111"/>
+      <c r="CD58" s="109"/>
       <c r="CF58" s="8"/>
-      <c r="CH58" s="112"/>
+      <c r="CH58" s="110"/>
     </row>
     <row r="59" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C59" s="122">
+      <c r="C59" s="125">
         <v>15</v>
       </c>
-      <c r="D59" s="122"/>
+      <c r="D59" s="125"/>
       <c r="E59" t="s">
         <v>693</v>
       </c>
@@ -16207,37 +16220,37 @@
       <c r="BV59" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX59" s="110"/>
+      <c r="BX59" s="108"/>
       <c r="BZ59" s="7"/>
       <c r="CB59" s="6"/>
-      <c r="CD59" s="111"/>
+      <c r="CD59" s="109"/>
       <c r="CF59" s="8"/>
-      <c r="CH59" s="112"/>
+      <c r="CH59" s="110"/>
       <c r="CI59" t="s">
         <v>614</v>
       </c>
     </row>
     <row r="60" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C60" s="122">
+      <c r="C60" s="125">
         <v>16</v>
       </c>
-      <c r="D60" s="122"/>
+      <c r="D60" s="125"/>
       <c r="E60" t="s">
         <v>565</v>
       </c>
       <c r="BV60" s="4"/>
-      <c r="BX60" s="110"/>
+      <c r="BX60" s="108"/>
       <c r="BZ60" s="7"/>
       <c r="CB60" s="6"/>
-      <c r="CD60" s="111"/>
+      <c r="CD60" s="109"/>
       <c r="CF60" s="8"/>
-      <c r="CH60" s="112"/>
+      <c r="CH60" s="110"/>
     </row>
     <row r="61" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C61" s="122">
+      <c r="C61" s="125">
         <v>17</v>
       </c>
-      <c r="D61" s="122"/>
+      <c r="D61" s="125"/>
       <c r="E61" t="s">
         <v>566</v>
       </c>
@@ -16247,43 +16260,43 @@
       <c r="BV61" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX61" s="110" t="s">
+      <c r="BX61" s="108" t="s">
         <v>35</v>
       </c>
       <c r="BZ61" s="7" t="s">
         <v>35</v>
       </c>
       <c r="CB61" s="6"/>
-      <c r="CD61" s="111" t="s">
+      <c r="CD61" s="109" t="s">
         <v>35</v>
       </c>
       <c r="CF61" s="8"/>
-      <c r="CH61" s="112"/>
+      <c r="CH61" s="110"/>
       <c r="CI61" t="s">
         <v>615</v>
       </c>
     </row>
     <row r="62" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C62" s="122">
+      <c r="C62" s="125">
         <v>18</v>
       </c>
-      <c r="D62" s="122"/>
+      <c r="D62" s="125"/>
       <c r="E62" t="s">
         <v>567</v>
       </c>
       <c r="BV62" s="4"/>
-      <c r="BX62" s="110"/>
+      <c r="BX62" s="108"/>
       <c r="BZ62" s="7"/>
       <c r="CB62" s="6"/>
-      <c r="CD62" s="111"/>
+      <c r="CD62" s="109"/>
       <c r="CF62" s="8"/>
-      <c r="CH62" s="112"/>
+      <c r="CH62" s="110"/>
     </row>
     <row r="63" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C63" s="122">
+      <c r="C63" s="125">
         <v>19</v>
       </c>
-      <c r="D63" s="122"/>
+      <c r="D63" s="125"/>
       <c r="E63" t="s">
         <v>695</v>
       </c>
@@ -16293,7 +16306,7 @@
       <c r="BV63" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX63" s="110" t="s">
+      <c r="BX63" s="108" t="s">
         <v>35</v>
       </c>
       <c r="BZ63" s="7" t="s">
@@ -16302,13 +16315,13 @@
       <c r="CB63" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CD63" s="111" t="s">
+      <c r="CD63" s="109" t="s">
         <v>35</v>
       </c>
       <c r="CF63" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="CH63" s="112" t="s">
+      <c r="CH63" s="110" t="s">
         <v>35</v>
       </c>
       <c r="CI63" t="s">
@@ -16316,20 +16329,20 @@
       </c>
     </row>
     <row r="64" spans="3:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C64" s="122">
+      <c r="C64" s="125">
         <v>20</v>
       </c>
-      <c r="D64" s="122"/>
+      <c r="D64" s="125"/>
       <c r="E64" t="s">
         <v>703</v>
       </c>
       <c r="BV64" s="4"/>
-      <c r="BX64" s="110"/>
+      <c r="BX64" s="108"/>
       <c r="BZ64" s="7"/>
       <c r="CB64" s="6"/>
-      <c r="CD64" s="111"/>
+      <c r="CD64" s="109"/>
       <c r="CF64" s="8"/>
-      <c r="CH64" s="112"/>
+      <c r="CH64" s="110"/>
     </row>
     <row r="65" spans="71:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="BS65" t="s">
@@ -16338,28 +16351,28 @@
       <c r="BV65" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX65" s="110"/>
+      <c r="BX65" s="108"/>
       <c r="BZ65" s="7" t="s">
         <v>35</v>
       </c>
       <c r="CB65" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CD65" s="111"/>
+      <c r="CD65" s="109"/>
       <c r="CF65" s="8"/>
-      <c r="CH65" s="112"/>
+      <c r="CH65" s="110"/>
       <c r="CI65" t="s">
         <v>617</v>
       </c>
     </row>
     <row r="66" spans="71:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="BV66" s="4"/>
-      <c r="BX66" s="110"/>
+      <c r="BX66" s="108"/>
       <c r="BZ66" s="7"/>
       <c r="CB66" s="6"/>
-      <c r="CD66" s="111"/>
+      <c r="CD66" s="109"/>
       <c r="CF66" s="8"/>
-      <c r="CH66" s="112"/>
+      <c r="CH66" s="110"/>
     </row>
     <row r="67" spans="71:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="BS67" t="s">
@@ -16368,7 +16381,7 @@
       <c r="BV67" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX67" s="110" t="s">
+      <c r="BX67" s="108" t="s">
         <v>35</v>
       </c>
       <c r="BZ67" s="7" t="s">
@@ -16377,23 +16390,23 @@
       <c r="CB67" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CD67" s="111" t="s">
+      <c r="CD67" s="109" t="s">
         <v>35</v>
       </c>
       <c r="CF67" s="8"/>
-      <c r="CH67" s="112"/>
+      <c r="CH67" s="110"/>
       <c r="CI67" t="s">
         <v>618</v>
       </c>
     </row>
     <row r="68" spans="71:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="BV68" s="4"/>
-      <c r="BX68" s="110"/>
+      <c r="BX68" s="108"/>
       <c r="BZ68" s="7"/>
       <c r="CB68" s="6"/>
-      <c r="CD68" s="111"/>
+      <c r="CD68" s="109"/>
       <c r="CF68" s="8"/>
-      <c r="CH68" s="112"/>
+      <c r="CH68" s="110"/>
     </row>
     <row r="69" spans="71:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="BS69" t="s">
@@ -16402,7 +16415,7 @@
       <c r="BV69" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX69" s="110" t="s">
+      <c r="BX69" s="108" t="s">
         <v>35</v>
       </c>
       <c r="BZ69" s="7" t="s">
@@ -16411,25 +16424,25 @@
       <c r="CB69" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CD69" s="111" t="s">
+      <c r="CD69" s="109" t="s">
         <v>35</v>
       </c>
       <c r="CF69" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="CH69" s="112"/>
+      <c r="CH69" s="110"/>
       <c r="CI69" t="s">
         <v>619</v>
       </c>
     </row>
     <row r="70" spans="71:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="BV70" s="4"/>
-      <c r="BX70" s="110"/>
+      <c r="BX70" s="108"/>
       <c r="BZ70" s="7"/>
       <c r="CB70" s="6"/>
-      <c r="CD70" s="111"/>
+      <c r="CD70" s="109"/>
       <c r="CF70" s="8"/>
-      <c r="CH70" s="112"/>
+      <c r="CH70" s="110"/>
     </row>
     <row r="71" spans="71:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="BS71" t="s">
@@ -16438,26 +16451,26 @@
       <c r="BV71" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX71" s="110"/>
+      <c r="BX71" s="108"/>
       <c r="BZ71" s="7" t="s">
         <v>35</v>
       </c>
       <c r="CB71" s="6"/>
-      <c r="CD71" s="111"/>
+      <c r="CD71" s="109"/>
       <c r="CF71" s="8"/>
-      <c r="CH71" s="112"/>
+      <c r="CH71" s="110"/>
       <c r="CI71" t="s">
         <v>620</v>
       </c>
     </row>
     <row r="72" spans="71:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="BV72" s="4"/>
-      <c r="BX72" s="110"/>
+      <c r="BX72" s="108"/>
       <c r="BZ72" s="7"/>
       <c r="CB72" s="6"/>
-      <c r="CD72" s="111"/>
+      <c r="CD72" s="109"/>
       <c r="CF72" s="8"/>
-      <c r="CH72" s="112"/>
+      <c r="CH72" s="110"/>
     </row>
     <row r="73" spans="71:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="BS73" t="s">
@@ -16466,26 +16479,26 @@
       <c r="BV73" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX73" s="110"/>
+      <c r="BX73" s="108"/>
       <c r="BZ73" s="7" t="s">
         <v>35</v>
       </c>
       <c r="CB73" s="6"/>
-      <c r="CD73" s="111"/>
+      <c r="CD73" s="109"/>
       <c r="CF73" s="8"/>
-      <c r="CH73" s="112"/>
+      <c r="CH73" s="110"/>
       <c r="CI73" t="s">
         <v>621</v>
       </c>
     </row>
     <row r="74" spans="71:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="BV74" s="4"/>
-      <c r="BX74" s="110"/>
+      <c r="BX74" s="108"/>
       <c r="BZ74" s="7"/>
       <c r="CB74" s="6"/>
-      <c r="CD74" s="111"/>
+      <c r="CD74" s="109"/>
       <c r="CF74" s="8"/>
-      <c r="CH74" s="112"/>
+      <c r="CH74" s="110"/>
     </row>
     <row r="75" spans="71:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="BS75" t="s">
@@ -16494,7 +16507,7 @@
       <c r="BV75" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX75" s="110" t="s">
+      <c r="BX75" s="108" t="s">
         <v>35</v>
       </c>
       <c r="BZ75" s="7" t="s">
@@ -16503,9 +16516,9 @@
       <c r="CB75" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CD75" s="111"/>
+      <c r="CD75" s="109"/>
       <c r="CF75" s="8"/>
-      <c r="CH75" s="112" t="s">
+      <c r="CH75" s="110" t="s">
         <v>35</v>
       </c>
       <c r="CI75" t="s">
@@ -16514,12 +16527,12 @@
     </row>
     <row r="76" spans="71:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="BV76" s="4"/>
-      <c r="BX76" s="110"/>
+      <c r="BX76" s="108"/>
       <c r="BZ76" s="7"/>
       <c r="CB76" s="6"/>
-      <c r="CD76" s="111"/>
+      <c r="CD76" s="109"/>
       <c r="CF76" s="8"/>
-      <c r="CH76" s="112"/>
+      <c r="CH76" s="110"/>
     </row>
     <row r="77" spans="71:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="BS77" t="s">
@@ -16528,16 +16541,16 @@
       <c r="BV77" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX77" s="110" t="s">
+      <c r="BX77" s="108" t="s">
         <v>35</v>
       </c>
       <c r="BZ77" s="7" t="s">
         <v>35</v>
       </c>
       <c r="CB77" s="6"/>
-      <c r="CD77" s="111"/>
+      <c r="CD77" s="109"/>
       <c r="CF77" s="8"/>
-      <c r="CH77" s="113" t="s">
+      <c r="CH77" s="111" t="s">
         <v>36</v>
       </c>
       <c r="CI77" t="s">
@@ -16546,12 +16559,12 @@
     </row>
     <row r="78" spans="71:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="BV78" s="4"/>
-      <c r="BX78" s="110"/>
+      <c r="BX78" s="108"/>
       <c r="BZ78" s="7"/>
       <c r="CB78" s="6"/>
-      <c r="CD78" s="111"/>
+      <c r="CD78" s="109"/>
       <c r="CF78" s="8"/>
-      <c r="CH78" s="112"/>
+      <c r="CH78" s="110"/>
     </row>
     <row r="79" spans="71:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="BS79" t="s">
@@ -16560,7 +16573,7 @@
       <c r="BV79" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX79" s="110" t="s">
+      <c r="BX79" s="108" t="s">
         <v>35</v>
       </c>
       <c r="BZ79" s="7" t="s">
@@ -16569,13 +16582,13 @@
       <c r="CB79" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CD79" s="111" t="s">
+      <c r="CD79" s="109" t="s">
         <v>35</v>
       </c>
       <c r="CF79" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="CH79" s="112" t="s">
+      <c r="CH79" s="110" t="s">
         <v>35</v>
       </c>
       <c r="CI79" t="s">
@@ -16584,12 +16597,12 @@
     </row>
     <row r="80" spans="71:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="BV80" s="4"/>
-      <c r="BX80" s="110"/>
+      <c r="BX80" s="108"/>
       <c r="BZ80" s="7"/>
       <c r="CB80" s="6"/>
-      <c r="CD80" s="111"/>
+      <c r="CD80" s="109"/>
       <c r="CF80" s="8"/>
-      <c r="CH80" s="112"/>
+      <c r="CH80" s="110"/>
     </row>
     <row r="81" spans="71:87" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="BS81" t="s">
@@ -16598,7 +16611,7 @@
       <c r="BV81" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BX81" s="110" t="s">
+      <c r="BX81" s="108" t="s">
         <v>35</v>
       </c>
       <c r="BZ81" s="7" t="s">
@@ -16607,13 +16620,13 @@
       <c r="CB81" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CD81" s="111" t="s">
+      <c r="CD81" s="109" t="s">
         <v>35</v>
       </c>
       <c r="CF81" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="CH81" s="112" t="s">
+      <c r="CH81" s="110" t="s">
         <v>35</v>
       </c>
       <c r="CI81" t="s">
@@ -16678,7 +16691,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D07260AB-7EDC-4D45-983A-4CD0B322649E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="E1:CK56"/>
   <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
@@ -16686,22 +16699,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="5:89" x14ac:dyDescent="0.4">
-      <c r="O1" s="123" t="s">
+      <c r="O1" s="126" t="s">
         <v>379</v>
       </c>
-      <c r="P1" s="123"/>
-      <c r="Q1" s="123"/>
-      <c r="R1" s="123"/>
+      <c r="P1" s="126"/>
+      <c r="Q1" s="126"/>
+      <c r="R1" s="126"/>
     </row>
     <row r="2" spans="5:89" x14ac:dyDescent="0.4">
-      <c r="N2" s="123" t="s">
+      <c r="N2" s="126" t="s">
         <v>380</v>
       </c>
-      <c r="O2" s="123"/>
-      <c r="P2" s="123"/>
-      <c r="Q2" s="123"/>
-      <c r="R2" s="123"/>
-      <c r="S2" s="123"/>
+      <c r="O2" s="126"/>
+      <c r="P2" s="126"/>
+      <c r="Q2" s="126"/>
+      <c r="R2" s="126"/>
+      <c r="S2" s="126"/>
     </row>
     <row r="3" spans="5:89" x14ac:dyDescent="0.4">
       <c r="P3" s="70"/>
@@ -17003,18 +17016,18 @@
       <c r="AH10" s="69" t="s">
         <v>178</v>
       </c>
-      <c r="AQ10" s="123" t="s">
+      <c r="AQ10" s="126" t="s">
         <v>707</v>
       </c>
-      <c r="AR10" s="123"/>
-      <c r="AZ10" s="123" t="s">
+      <c r="AR10" s="126"/>
+      <c r="AZ10" s="126" t="s">
         <v>705</v>
       </c>
-      <c r="BA10" s="123"/>
-      <c r="BI10" s="123" t="s">
+      <c r="BA10" s="126"/>
+      <c r="BI10" s="126" t="s">
         <v>3</v>
       </c>
-      <c r="BJ10" s="123"/>
+      <c r="BJ10" s="126"/>
       <c r="BS10" s="80"/>
       <c r="BT10" s="74"/>
       <c r="BU10" s="78"/>
@@ -17034,26 +17047,26 @@
       <c r="G11" s="69" t="s">
         <v>167</v>
       </c>
-      <c r="AE11" s="123" t="s">
+      <c r="AE11" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="AF11" s="123"/>
-      <c r="AQ11" s="123" t="s">
+      <c r="AF11" s="126"/>
+      <c r="AQ11" s="126" t="s">
         <v>708</v>
       </c>
-      <c r="AR11" s="123"/>
-      <c r="AY11" s="123" t="s">
+      <c r="AR11" s="126"/>
+      <c r="AY11" s="126" t="s">
         <v>706</v>
       </c>
-      <c r="AZ11" s="123"/>
-      <c r="BA11" s="123"/>
-      <c r="BB11" s="123"/>
-      <c r="BH11" s="123" t="s">
+      <c r="AZ11" s="126"/>
+      <c r="BA11" s="126"/>
+      <c r="BB11" s="126"/>
+      <c r="BH11" s="126" t="s">
         <v>186</v>
       </c>
-      <c r="BI11" s="123"/>
-      <c r="BJ11" s="123"/>
-      <c r="BK11" s="123"/>
+      <c r="BI11" s="126"/>
+      <c r="BJ11" s="126"/>
+      <c r="BK11" s="126"/>
       <c r="BR11" s="80"/>
       <c r="BS11" s="74"/>
       <c r="BT11" s="74"/>
@@ -17070,10 +17083,10 @@
       </c>
     </row>
     <row r="12" spans="5:89" x14ac:dyDescent="0.4">
-      <c r="AE12" s="123" t="s">
+      <c r="AE12" s="126" t="s">
         <v>185</v>
       </c>
-      <c r="AF12" s="123"/>
+      <c r="AF12" s="126"/>
       <c r="AQ12" s="69" t="s">
         <v>715</v>
       </c>
@@ -17090,19 +17103,19 @@
     </row>
     <row r="13" spans="5:89" x14ac:dyDescent="0.4">
       <c r="BQ13" s="89"/>
-      <c r="BX13" s="123" t="s">
+      <c r="BX13" s="126" t="s">
         <v>4</v>
       </c>
-      <c r="BY13" s="123"/>
+      <c r="BY13" s="126"/>
       <c r="CH13" s="69" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="14" spans="5:89" x14ac:dyDescent="0.4">
-      <c r="BX14" s="123" t="s">
+      <c r="BX14" s="126" t="s">
         <v>187</v>
       </c>
-      <c r="BY14" s="123"/>
+      <c r="BY14" s="126"/>
     </row>
     <row r="15" spans="5:89" x14ac:dyDescent="0.4">
       <c r="V15" s="71"/>
@@ -17329,67 +17342,67 @@
       <c r="BF19" s="74"/>
       <c r="BG19" s="74"/>
       <c r="BH19" s="79"/>
-      <c r="BR19" s="123" t="s">
+      <c r="BR19" s="126" t="s">
         <v>15</v>
       </c>
-      <c r="BS19" s="123"/>
-      <c r="CA19" s="123" t="s">
+      <c r="BS19" s="126"/>
+      <c r="CA19" s="126" t="s">
         <v>17</v>
       </c>
-      <c r="CB19" s="123"/>
+      <c r="CB19" s="126"/>
     </row>
     <row r="20" spans="7:89" x14ac:dyDescent="0.4">
-      <c r="L20" s="123" t="s">
+      <c r="L20" s="126" t="s">
         <v>177</v>
       </c>
-      <c r="M20" s="123"/>
-      <c r="W20" s="123" t="s">
+      <c r="M20" s="126"/>
+      <c r="W20" s="126" t="s">
         <v>6</v>
       </c>
-      <c r="X20" s="123"/>
-      <c r="AI20" s="123" t="s">
+      <c r="X20" s="126"/>
+      <c r="AI20" s="126" t="s">
         <v>672</v>
       </c>
-      <c r="AJ20" s="123"/>
-      <c r="AR20" s="123" t="s">
+      <c r="AJ20" s="126"/>
+      <c r="AR20" s="126" t="s">
         <v>11</v>
       </c>
-      <c r="AS20" s="123"/>
+      <c r="AS20" s="126"/>
       <c r="BI20" s="70"/>
-      <c r="BR20" s="123" t="s">
+      <c r="BR20" s="126" t="s">
         <v>192</v>
       </c>
-      <c r="BS20" s="123"/>
-      <c r="BZ20" s="123" t="s">
+      <c r="BS20" s="126"/>
+      <c r="BZ20" s="126" t="s">
         <v>193</v>
       </c>
-      <c r="CA20" s="123"/>
-      <c r="CB20" s="123"/>
-      <c r="CC20" s="123"/>
+      <c r="CA20" s="126"/>
+      <c r="CB20" s="126"/>
+      <c r="CC20" s="126"/>
     </row>
     <row r="21" spans="7:89" x14ac:dyDescent="0.4">
-      <c r="K21" s="123" t="s">
+      <c r="K21" s="126" t="s">
         <v>188</v>
       </c>
-      <c r="L21" s="123"/>
-      <c r="M21" s="123"/>
-      <c r="N21" s="123"/>
-      <c r="W21" s="123" t="s">
+      <c r="L21" s="126"/>
+      <c r="M21" s="126"/>
+      <c r="N21" s="126"/>
+      <c r="W21" s="126" t="s">
         <v>189</v>
       </c>
-      <c r="X21" s="123"/>
-      <c r="AI21" s="123" t="s">
+      <c r="X21" s="126"/>
+      <c r="AI21" s="126" t="s">
         <v>673</v>
       </c>
-      <c r="AJ21" s="123"/>
-      <c r="AR21" s="123" t="s">
+      <c r="AJ21" s="126"/>
+      <c r="AR21" s="126" t="s">
         <v>190</v>
       </c>
-      <c r="AS21" s="123"/>
-      <c r="BE21" s="123" t="s">
+      <c r="AS21" s="126"/>
+      <c r="BE21" s="126" t="s">
         <v>13</v>
       </c>
-      <c r="BF21" s="123"/>
+      <c r="BF21" s="126"/>
       <c r="BJ21" s="69" t="s">
         <v>179</v>
       </c>
@@ -17407,13 +17420,28 @@
       <c r="AR22" s="69" t="s">
         <v>717</v>
       </c>
-      <c r="BE22" s="123" t="s">
+      <c r="BE22" s="126" t="s">
         <v>191</v>
       </c>
-      <c r="BF22" s="123"/>
+      <c r="BF22" s="126"/>
       <c r="BR22" s="69" t="s">
         <v>722</v>
       </c>
+    </row>
+    <row r="24" spans="7:89" x14ac:dyDescent="0.2">
+      <c r="BP24" s="124" t="s">
+        <v>734</v>
+      </c>
+      <c r="BQ24" s="121"/>
+    </row>
+    <row r="25" spans="7:89" x14ac:dyDescent="0.4">
+      <c r="BL25" s="74"/>
+      <c r="BM25" s="74"/>
+      <c r="BN25" s="74"/>
+      <c r="BO25" s="74" t="s">
+        <v>732</v>
+      </c>
+      <c r="BP25" s="70"/>
     </row>
     <row r="26" spans="7:89" x14ac:dyDescent="0.4">
       <c r="AD26" s="69" t="s">
@@ -17423,22 +17451,16 @@
       <c r="AK26" s="71"/>
       <c r="AL26" s="71"/>
       <c r="AM26" s="71"/>
-      <c r="AN26" s="72"/>
-      <c r="BI26" s="71"/>
-      <c r="BJ26" s="71"/>
-      <c r="BK26" s="71"/>
-      <c r="BL26" s="71"/>
-      <c r="BM26" s="72" t="s">
-        <v>168</v>
-      </c>
-      <c r="BR26" s="68"/>
-      <c r="BS26" s="68"/>
-      <c r="BT26" s="68"/>
-      <c r="BU26" s="68"/>
-      <c r="BV26" s="68"/>
-      <c r="BW26" s="68"/>
-      <c r="BX26" s="68"/>
-      <c r="BY26" s="68"/>
+      <c r="AN26" s="71"/>
+      <c r="AO26" s="71"/>
+      <c r="AP26" s="71"/>
+      <c r="BK26" s="76"/>
+      <c r="BL26" s="74"/>
+      <c r="BM26" s="74"/>
+      <c r="BN26" s="74"/>
+      <c r="BO26" s="74"/>
+      <c r="BP26" s="70"/>
+      <c r="BQ26" s="70"/>
     </row>
     <row r="27" spans="7:89" x14ac:dyDescent="0.4">
       <c r="G27" s="68"/>
@@ -17470,51 +17492,45 @@
       <c r="AE27" s="68"/>
       <c r="AF27" s="68"/>
       <c r="AG27" s="68"/>
-      <c r="AH27" s="68"/>
-      <c r="AI27" s="80"/>
-      <c r="AJ27" s="71"/>
-      <c r="AK27" s="71"/>
+      <c r="AH27" s="76"/>
+      <c r="AI27" s="84"/>
+      <c r="AJ27" s="68"/>
       <c r="AL27" s="71"/>
       <c r="AM27" s="71"/>
-      <c r="AN27" s="70"/>
-      <c r="AO27" s="68"/>
-      <c r="AQ27" s="68"/>
-      <c r="AR27" s="68"/>
+      <c r="AN27" s="71"/>
+      <c r="AO27" s="71"/>
+      <c r="AP27" s="76"/>
+      <c r="AQ27" s="70"/>
       <c r="AS27" s="68"/>
       <c r="AT27" s="68"/>
       <c r="AU27" s="68"/>
       <c r="AV27" s="68"/>
       <c r="AW27" s="68"/>
       <c r="AX27" s="68"/>
-      <c r="AY27" s="68" t="s">
-        <v>168</v>
-      </c>
+      <c r="AY27" s="68"/>
       <c r="AZ27" s="68"/>
-      <c r="BA27" s="68"/>
+      <c r="BA27" s="68" t="s">
+        <v>733</v>
+      </c>
       <c r="BB27" s="68"/>
       <c r="BC27" s="68"/>
       <c r="BD27" s="68"/>
       <c r="BE27" s="68"/>
       <c r="BF27" s="68"/>
       <c r="BG27" s="68"/>
-      <c r="BH27" s="80"/>
-      <c r="BI27" s="71"/>
-      <c r="BJ27" s="71"/>
-      <c r="BK27" s="71"/>
-      <c r="BL27" s="71"/>
-      <c r="BM27" s="75"/>
-      <c r="BN27" s="68"/>
-      <c r="BO27" s="68"/>
-      <c r="BP27" s="68"/>
-      <c r="BQ27" s="80"/>
-      <c r="BR27" s="71"/>
-      <c r="BS27" s="71"/>
-      <c r="BT27" s="71"/>
-      <c r="BU27" s="71"/>
-      <c r="BV27" s="71"/>
-      <c r="BW27" s="71"/>
-      <c r="BX27" s="71"/>
-      <c r="BY27" s="71"/>
+      <c r="BH27" s="68"/>
+      <c r="BI27" s="68"/>
+      <c r="BJ27" s="80"/>
+      <c r="BK27" s="76"/>
+      <c r="BP27" s="70"/>
+      <c r="BQ27" s="70"/>
+      <c r="BR27" s="70"/>
+      <c r="BX27" s="80"/>
+      <c r="BY27" s="74"/>
+      <c r="BZ27" s="74"/>
+      <c r="CA27" s="74"/>
+      <c r="CB27" s="74"/>
+      <c r="CC27" s="74"/>
     </row>
     <row r="28" spans="7:89" x14ac:dyDescent="0.4">
       <c r="G28" s="71"/>
@@ -17543,19 +17559,15 @@
       <c r="AD28" s="71"/>
       <c r="AE28" s="71"/>
       <c r="AF28" s="71"/>
-      <c r="AG28" s="82"/>
-      <c r="AH28" s="71"/>
-      <c r="AJ28" s="74"/>
-      <c r="AK28" s="74"/>
-      <c r="AL28" s="74"/>
+      <c r="AG28" s="71"/>
+      <c r="AJ28" s="71"/>
+      <c r="AK28" s="82"/>
       <c r="AM28" s="74"/>
       <c r="AN28" s="74"/>
-      <c r="AO28" s="71"/>
-      <c r="AP28" s="82"/>
-      <c r="AQ28" s="71"/>
-      <c r="AR28" s="71"/>
-      <c r="AS28" s="71"/>
-      <c r="AT28" s="71"/>
+      <c r="AO28" s="74"/>
+      <c r="AR28" s="92"/>
+      <c r="AS28" s="74"/>
+      <c r="AT28" s="82"/>
       <c r="AU28" s="71"/>
       <c r="AV28" s="71"/>
       <c r="AW28" s="71"/>
@@ -17564,29 +17576,24 @@
       <c r="AZ28" s="71"/>
       <c r="BA28" s="71"/>
       <c r="BB28" s="71"/>
-      <c r="BC28" s="78"/>
+      <c r="BC28" s="71"/>
       <c r="BD28" s="71"/>
-      <c r="BE28" s="71"/>
-      <c r="BF28" s="79"/>
+      <c r="BE28" s="78"/>
+      <c r="BF28" s="71"/>
       <c r="BG28" s="71"/>
-      <c r="BH28" s="71"/>
+      <c r="BH28" s="79"/>
       <c r="BI28" s="71"/>
-      <c r="BJ28" s="71"/>
-      <c r="BK28" s="71"/>
-      <c r="BL28" s="71"/>
-      <c r="BM28" s="71"/>
-      <c r="BN28" s="71"/>
-      <c r="BO28" s="82"/>
-      <c r="BP28" s="71"/>
-      <c r="BQ28" s="71"/>
-      <c r="BR28" s="71"/>
-      <c r="BS28" s="71"/>
-      <c r="BT28" s="71"/>
-      <c r="BU28" s="71"/>
-      <c r="BV28" s="71"/>
-      <c r="BW28" s="71"/>
-      <c r="BX28" s="71"/>
-      <c r="BY28" s="71"/>
+      <c r="BJ28" s="74"/>
+      <c r="BK28" s="76"/>
+      <c r="BL28" s="92"/>
+      <c r="BM28" s="92"/>
+      <c r="BN28" s="92"/>
+      <c r="BO28" s="92"/>
+      <c r="BP28" s="70"/>
+      <c r="BQ28" s="70"/>
+      <c r="BR28" s="75"/>
+      <c r="BS28" s="70"/>
+      <c r="BW28" s="80"/>
     </row>
     <row r="29" spans="7:89" x14ac:dyDescent="0.4">
       <c r="M29" s="84"/>
@@ -17598,124 +17605,129 @@
       <c r="AC29" s="69" t="s">
         <v>178</v>
       </c>
-      <c r="AI29" s="84"/>
-      <c r="AJ29" s="74"/>
-      <c r="AK29" s="74"/>
+      <c r="AH29" s="70"/>
+      <c r="AI29" s="80"/>
+      <c r="AJ29" s="71"/>
+      <c r="AK29" s="71"/>
       <c r="AL29" s="74"/>
       <c r="AM29" s="74"/>
-      <c r="AN29" s="76"/>
-      <c r="BE29" s="84"/>
-      <c r="BH29" s="84"/>
-      <c r="BI29" s="74"/>
-      <c r="BJ29" s="74"/>
-      <c r="BK29" s="74"/>
-      <c r="BL29" s="74"/>
-      <c r="BM29" s="76"/>
-      <c r="BQ29" s="84"/>
-      <c r="BR29" s="68"/>
-      <c r="BS29" s="68"/>
-      <c r="BT29" s="68"/>
-      <c r="BU29" s="68"/>
-      <c r="BV29" s="68"/>
-      <c r="BW29" s="68"/>
-      <c r="BX29" s="68"/>
-      <c r="BY29" s="68"/>
+      <c r="AN29" s="74"/>
+      <c r="AO29" s="74"/>
+      <c r="AP29" s="75"/>
+      <c r="AQ29" s="71"/>
+      <c r="AR29" s="76"/>
+      <c r="BG29" s="84"/>
+      <c r="BK29" s="70"/>
+      <c r="BL29" s="71"/>
+      <c r="BM29" s="71"/>
+      <c r="BN29" s="71"/>
+      <c r="BO29" s="71"/>
+      <c r="BP29" s="71"/>
+      <c r="BQ29" s="75"/>
+      <c r="BR29" s="71"/>
+      <c r="BS29" s="74"/>
+      <c r="BT29" s="74"/>
+      <c r="BU29" s="82"/>
+      <c r="BV29" s="74"/>
+      <c r="BW29" s="74"/>
+      <c r="BX29" s="74"/>
+      <c r="BY29" s="74"/>
+      <c r="BZ29" s="74"/>
+      <c r="CA29" s="74"/>
+      <c r="CB29" s="74"/>
+      <c r="CC29" s="74"/>
     </row>
     <row r="30" spans="7:89" x14ac:dyDescent="0.4">
-      <c r="AK30" s="124" t="s">
+      <c r="AM30" s="127" t="s">
         <v>23</v>
       </c>
-      <c r="AL30" s="124"/>
-      <c r="AN30" s="69" t="s">
+      <c r="AN30" s="127"/>
+      <c r="AP30" s="69" t="s">
         <v>178</v>
       </c>
-      <c r="AV30" s="123" t="s">
+      <c r="AX30" s="126" t="s">
         <v>24</v>
       </c>
-      <c r="AW30" s="123"/>
-      <c r="BF30" s="75"/>
-      <c r="BG30" s="71"/>
-      <c r="BH30" s="71"/>
+      <c r="AY30" s="126"/>
+      <c r="BH30" s="70"/>
       <c r="BI30" s="71"/>
-      <c r="BJ30" s="125" t="s">
+      <c r="BL30" s="120"/>
+      <c r="BM30" s="128" t="s">
         <v>25</v>
       </c>
-      <c r="BK30" s="125"/>
-      <c r="BL30" s="71"/>
-      <c r="BM30" s="72" t="s">
+      <c r="BN30" s="128"/>
+      <c r="BO30" s="72" t="s">
         <v>168</v>
       </c>
-      <c r="BR30" s="69" t="s">
+      <c r="BW30" s="69" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="31" spans="7:89" x14ac:dyDescent="0.4">
-      <c r="O31" s="123" t="s">
+      <c r="O31" s="126" t="s">
         <v>19</v>
       </c>
-      <c r="P31" s="123"/>
-      <c r="Z31" s="123" t="s">
+      <c r="P31" s="126"/>
+      <c r="Z31" s="126" t="s">
         <v>21</v>
       </c>
-      <c r="AA31" s="123"/>
-      <c r="AJ31" s="71"/>
-      <c r="AK31" s="71"/>
+      <c r="AA31" s="126"/>
       <c r="AL31" s="71"/>
       <c r="AM31" s="71"/>
-      <c r="AN31" s="72" t="s">
+      <c r="AN31" s="71"/>
+      <c r="AO31" s="71"/>
+      <c r="AP31" s="72" t="s">
         <v>168</v>
       </c>
-      <c r="AS31" s="71"/>
-      <c r="AT31" s="71"/>
       <c r="AU31" s="71"/>
       <c r="AV31" s="71"/>
       <c r="AW31" s="71"/>
       <c r="AX31" s="71"/>
-      <c r="AY31" s="68" t="s">
+      <c r="AY31" s="71"/>
+      <c r="AZ31" s="71"/>
+      <c r="BA31" s="68" t="s">
         <v>168</v>
       </c>
-      <c r="AZ31" s="71"/>
-      <c r="BD31" s="71"/>
-      <c r="BE31" s="80"/>
+      <c r="BB31" s="71"/>
       <c r="BF31" s="71"/>
-      <c r="BG31" s="71"/>
-      <c r="BH31" s="78"/>
+      <c r="BG31" s="80"/>
+      <c r="BH31" s="74"/>
       <c r="BI31" s="71"/>
-      <c r="BJ31" s="71"/>
-      <c r="BK31" s="71"/>
-      <c r="BL31" s="71"/>
-      <c r="BM31" s="75"/>
+      <c r="BJ31" s="78"/>
+      <c r="BK31" s="74"/>
+      <c r="BL31" s="74"/>
+      <c r="BM31" s="74"/>
+      <c r="BN31" s="74"/>
+      <c r="BO31" s="75"/>
     </row>
     <row r="32" spans="7:89" x14ac:dyDescent="0.4">
-      <c r="M32" s="123" t="s">
+      <c r="M32" s="126" t="s">
         <v>642</v>
       </c>
-      <c r="N32" s="123"/>
-      <c r="O32" s="123"/>
-      <c r="P32" s="123"/>
-      <c r="Q32" s="123"/>
-      <c r="R32" s="123"/>
-      <c r="Y32" s="123" t="s">
+      <c r="N32" s="126"/>
+      <c r="O32" s="126"/>
+      <c r="P32" s="126"/>
+      <c r="Q32" s="126"/>
+      <c r="R32" s="126"/>
+      <c r="Y32" s="126" t="s">
         <v>194</v>
       </c>
-      <c r="Z32" s="123"/>
-      <c r="AA32" s="123"/>
-      <c r="AB32" s="123"/>
-      <c r="AE32" s="71"/>
-      <c r="AF32" s="68"/>
-      <c r="AG32" s="68"/>
+      <c r="Z32" s="126"/>
+      <c r="AA32" s="126"/>
+      <c r="AB32" s="126"/>
+      <c r="AG32" s="71"/>
       <c r="AH32" s="68"/>
-      <c r="AI32" s="80"/>
-      <c r="AJ32" s="71"/>
-      <c r="AK32" s="71"/>
+      <c r="AI32" s="68"/>
+      <c r="AJ32" s="68"/>
+      <c r="AK32" s="80"/>
       <c r="AL32" s="71"/>
       <c r="AM32" s="71"/>
-      <c r="AN32" s="70"/>
-      <c r="AO32" s="68"/>
+      <c r="AN32" s="71"/>
+      <c r="AO32" s="71"/>
+      <c r="AP32" s="70"/>
       <c r="AQ32" s="68"/>
-      <c r="AR32" s="76"/>
-      <c r="AT32" s="74"/>
-      <c r="AU32" s="74"/>
+      <c r="AS32" s="68"/>
+      <c r="AT32" s="76"/>
       <c r="AV32" s="74"/>
       <c r="AW32" s="74"/>
       <c r="AX32" s="74"/>
@@ -17723,7 +17735,7 @@
       <c r="AZ32" s="74"/>
       <c r="BA32" s="74"/>
       <c r="BB32" s="74"/>
-      <c r="BC32" s="82"/>
+      <c r="BC32" s="74"/>
       <c r="BD32" s="74"/>
       <c r="BE32" s="74"/>
       <c r="BF32" s="74"/>
@@ -17733,131 +17745,134 @@
       <c r="BJ32" s="74"/>
       <c r="BK32" s="74"/>
       <c r="BL32" s="74"/>
-      <c r="BN32" s="70"/>
-      <c r="BP32" s="69" t="s">
+      <c r="BM32" s="74"/>
+      <c r="BN32" s="74"/>
+      <c r="BP32" s="70"/>
+      <c r="BR32" s="69" t="s">
         <v>181</v>
       </c>
-      <c r="BR32" s="69" t="s">
+      <c r="BT32" s="69" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="33" spans="6:70" x14ac:dyDescent="0.4">
+    <row r="33" spans="6:72" x14ac:dyDescent="0.4">
       <c r="O33" s="69" t="s">
         <v>723</v>
       </c>
       <c r="Z33" s="69" t="s">
         <v>724</v>
       </c>
-      <c r="AD33" s="76"/>
-      <c r="AF33" s="71"/>
-      <c r="AG33" s="82"/>
+      <c r="AF33" s="76"/>
       <c r="AH33" s="71"/>
-      <c r="AJ33" s="74"/>
-      <c r="AK33" s="74"/>
+      <c r="AI33" s="82"/>
+      <c r="AJ33" s="71"/>
       <c r="AL33" s="74"/>
       <c r="AM33" s="74"/>
       <c r="AN33" s="74"/>
-      <c r="AO33" s="71"/>
-      <c r="AP33" s="82"/>
+      <c r="AO33" s="74"/>
+      <c r="AP33" s="74"/>
       <c r="AQ33" s="71"/>
-      <c r="AR33" s="71"/>
-      <c r="AS33" s="76"/>
-      <c r="BF33" s="84"/>
-      <c r="BG33" s="74"/>
-      <c r="BH33" s="74"/>
+      <c r="AR33" s="82"/>
+      <c r="AS33" s="71"/>
+      <c r="AT33" s="71"/>
+      <c r="AU33" s="76"/>
+      <c r="BH33" s="84"/>
       <c r="BI33" s="74"/>
       <c r="BJ33" s="74"/>
-      <c r="BK33" s="85"/>
-      <c r="BM33" s="70"/>
-      <c r="BO33" s="90"/>
-      <c r="BQ33" s="69" t="s">
+      <c r="BK33" s="74"/>
+      <c r="BL33" s="74"/>
+      <c r="BM33" s="85"/>
+      <c r="BO33" s="70"/>
+      <c r="BP33" s="123"/>
+      <c r="BQ33" s="70"/>
+      <c r="BS33" s="69" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="34" spans="6:70" x14ac:dyDescent="0.4">
-      <c r="AC34" s="76"/>
+    <row r="34" spans="6:72" x14ac:dyDescent="0.4">
       <c r="AE34" s="76"/>
-      <c r="AI34" s="84"/>
-      <c r="AJ34" s="74"/>
-      <c r="AK34" s="74"/>
+      <c r="AG34" s="76"/>
+      <c r="AK34" s="84"/>
       <c r="AL34" s="74"/>
       <c r="AM34" s="74"/>
-      <c r="AN34" s="76"/>
-      <c r="BN34" s="91"/>
-      <c r="BP34" s="70"/>
-    </row>
-    <row r="35" spans="6:70" x14ac:dyDescent="0.4">
-      <c r="AB35" s="123" t="s">
+      <c r="AN34" s="74"/>
+      <c r="AO34" s="74"/>
+      <c r="AP34" s="76"/>
+      <c r="BP34" s="122"/>
+      <c r="BR34" s="70"/>
+    </row>
+    <row r="35" spans="6:72" x14ac:dyDescent="0.4">
+      <c r="AB35" s="126" t="s">
         <v>182</v>
       </c>
-      <c r="AC35" s="123"/>
-      <c r="AD35" s="123"/>
-      <c r="AE35" s="123"/>
-      <c r="AT35" s="123" t="s">
+      <c r="AC35" s="126"/>
+      <c r="AD35" s="126"/>
+      <c r="AE35" s="126"/>
+      <c r="AT35" s="126" t="s">
         <v>196</v>
       </c>
-      <c r="AU35" s="123"/>
-      <c r="AV35" s="123"/>
-      <c r="AW35" s="123"/>
-      <c r="AX35" s="123"/>
-      <c r="AY35" s="123"/>
-      <c r="BH35" s="123" t="s">
+      <c r="AU35" s="126"/>
+      <c r="AV35" s="126"/>
+      <c r="AW35" s="126"/>
+      <c r="AX35" s="126"/>
+      <c r="AY35" s="126"/>
+      <c r="BH35" s="126" t="s">
         <v>641</v>
       </c>
-      <c r="BI35" s="123"/>
-      <c r="BJ35" s="123"/>
-      <c r="BK35" s="123"/>
-      <c r="BL35" s="123"/>
-      <c r="BM35" s="123"/>
-      <c r="BO35" s="70"/>
+      <c r="BI35" s="126"/>
+      <c r="BJ35" s="126"/>
+      <c r="BK35" s="126"/>
+      <c r="BL35" s="126"/>
+      <c r="BM35" s="126"/>
       <c r="BQ35" s="70"/>
-    </row>
-    <row r="36" spans="6:70" x14ac:dyDescent="0.4">
-      <c r="AB36" s="123" t="s">
+      <c r="BS35" s="70"/>
+    </row>
+    <row r="36" spans="6:72" x14ac:dyDescent="0.4">
+      <c r="AB36" s="126" t="s">
         <v>183</v>
       </c>
-      <c r="AC36" s="123"/>
-      <c r="AD36" s="123"/>
-      <c r="AE36" s="123"/>
-      <c r="AJ36" s="123" t="s">
+      <c r="AC36" s="126"/>
+      <c r="AD36" s="126"/>
+      <c r="AE36" s="126"/>
+      <c r="AJ36" s="126" t="s">
         <v>195</v>
       </c>
-      <c r="AK36" s="123"/>
-      <c r="AL36" s="123"/>
-      <c r="AM36" s="123"/>
+      <c r="AK36" s="126"/>
+      <c r="AL36" s="126"/>
+      <c r="AM36" s="126"/>
       <c r="AV36" s="69" t="s">
         <v>730</v>
       </c>
       <c r="BJ36" s="69" t="s">
         <v>731</v>
       </c>
-      <c r="BO36" s="123" t="s">
+      <c r="BQ36" s="126" t="s">
         <v>180</v>
       </c>
-      <c r="BP36" s="123"/>
-      <c r="BQ36" s="123"/>
-      <c r="BR36" s="123"/>
-    </row>
-    <row r="37" spans="6:70" x14ac:dyDescent="0.4">
+      <c r="BR36" s="126"/>
+      <c r="BS36" s="126"/>
+      <c r="BT36" s="126"/>
+    </row>
+    <row r="37" spans="6:72" x14ac:dyDescent="0.4">
       <c r="AC37" s="69" t="s">
         <v>729</v>
       </c>
       <c r="AK37" s="69" t="s">
         <v>726</v>
       </c>
-      <c r="BO37" s="123" t="s">
+      <c r="BQ37" s="126" t="s">
         <v>184</v>
       </c>
-      <c r="BP37" s="123"/>
-      <c r="BQ37" s="123"/>
-      <c r="BR37" s="123"/>
-    </row>
-    <row r="38" spans="6:70" x14ac:dyDescent="0.4">
-      <c r="BP38" s="69" t="s">
+      <c r="BR37" s="126"/>
+      <c r="BS37" s="126"/>
+      <c r="BT37" s="126"/>
+    </row>
+    <row r="38" spans="6:72" x14ac:dyDescent="0.4">
+      <c r="BR38" s="69" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="42" spans="6:70" x14ac:dyDescent="0.4">
+    <row r="42" spans="6:72" x14ac:dyDescent="0.4">
       <c r="L42" s="71"/>
       <c r="M42" s="71"/>
       <c r="N42" s="71"/>
@@ -17866,7 +17881,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="43" spans="6:70" x14ac:dyDescent="0.4">
+    <row r="43" spans="6:72" x14ac:dyDescent="0.4">
       <c r="F43" s="68"/>
       <c r="H43" s="68"/>
       <c r="I43" s="68"/>
@@ -17912,7 +17927,7 @@
       <c r="AX43" s="68"/>
       <c r="AY43" s="68"/>
     </row>
-    <row r="44" spans="6:70" x14ac:dyDescent="0.4">
+    <row r="44" spans="6:72" x14ac:dyDescent="0.4">
       <c r="F44" s="71"/>
       <c r="G44" s="82"/>
       <c r="H44" s="71"/>
@@ -17960,7 +17975,7 @@
       <c r="AX44" s="71"/>
       <c r="AY44" s="71"/>
     </row>
-    <row r="45" spans="6:70" x14ac:dyDescent="0.25">
+    <row r="45" spans="6:72" x14ac:dyDescent="0.25">
       <c r="I45" s="84"/>
       <c r="J45" s="74"/>
       <c r="K45" s="74"/>
@@ -17988,12 +18003,12 @@
       <c r="AL45" s="68"/>
       <c r="AM45" s="68"/>
       <c r="AN45" s="68"/>
-      <c r="AO45" s="92" t="s">
+      <c r="AO45" s="90" t="s">
         <v>388</v>
       </c>
-      <c r="AP45" s="92"/>
-    </row>
-    <row r="46" spans="6:70" x14ac:dyDescent="0.25">
+      <c r="AP45" s="90"/>
+    </row>
+    <row r="46" spans="6:72" x14ac:dyDescent="0.25">
       <c r="K46" s="84"/>
       <c r="L46" s="74"/>
       <c r="M46" s="74"/>
@@ -18022,12 +18037,12 @@
       <c r="AJ46" s="71"/>
       <c r="AK46" s="71"/>
       <c r="AL46" s="71"/>
-      <c r="AO46" s="92" t="s">
+      <c r="AO46" s="90" t="s">
         <v>388</v>
       </c>
-      <c r="AP46" s="92"/>
-    </row>
-    <row r="47" spans="6:70" x14ac:dyDescent="0.25">
+      <c r="AP46" s="90"/>
+    </row>
+    <row r="47" spans="6:72" x14ac:dyDescent="0.25">
       <c r="Q47" s="84"/>
       <c r="R47" s="71"/>
       <c r="S47" s="71"/>
@@ -18051,16 +18066,16 @@
       <c r="AL47" s="74"/>
       <c r="AM47" s="74"/>
       <c r="AN47" s="74"/>
-      <c r="AO47" s="92" t="s">
+      <c r="AO47" s="90" t="s">
         <v>388</v>
       </c>
-      <c r="AP47" s="92"/>
-    </row>
-    <row r="48" spans="6:70" x14ac:dyDescent="0.25">
-      <c r="M48" s="123" t="s">
+      <c r="AP47" s="90"/>
+    </row>
+    <row r="48" spans="6:72" x14ac:dyDescent="0.25">
+      <c r="M48" s="126" t="s">
         <v>13</v>
       </c>
-      <c r="N48" s="123"/>
+      <c r="N48" s="126"/>
       <c r="V48" s="84"/>
       <c r="X48" s="74"/>
       <c r="Y48" s="74"/>
@@ -18077,16 +18092,16 @@
       <c r="AJ48" s="74"/>
       <c r="AK48" s="74"/>
       <c r="AL48" s="74"/>
-      <c r="AM48" s="93" t="s">
+      <c r="AM48" s="91" t="s">
         <v>383</v>
       </c>
-      <c r="AP48" s="92"/>
+      <c r="AP48" s="90"/>
     </row>
     <row r="49" spans="13:42" x14ac:dyDescent="0.25">
-      <c r="M49" s="123" t="s">
+      <c r="M49" s="126" t="s">
         <v>191</v>
       </c>
-      <c r="N49" s="123"/>
+      <c r="N49" s="126"/>
       <c r="W49" s="84"/>
       <c r="Y49" s="74"/>
       <c r="Z49" s="74"/>
@@ -18102,14 +18117,14 @@
       <c r="AJ49" s="74"/>
       <c r="AK49" s="74"/>
       <c r="AL49" s="74"/>
-      <c r="AM49" s="92" t="s">
+      <c r="AM49" s="90" t="s">
         <v>383</v>
       </c>
-      <c r="AP49" s="92"/>
+      <c r="AP49" s="90"/>
     </row>
     <row r="50" spans="13:42" x14ac:dyDescent="0.25">
       <c r="X50" s="84"/>
-      <c r="Y50" s="94"/>
+      <c r="Y50" s="92"/>
       <c r="Z50" s="74"/>
       <c r="AA50" s="74"/>
       <c r="AB50" s="74"/>
@@ -18122,10 +18137,10 @@
       <c r="AI50" s="74"/>
       <c r="AJ50" s="74"/>
       <c r="AK50" s="74"/>
-      <c r="AL50" s="92" t="s">
+      <c r="AL50" s="90" t="s">
         <v>381</v>
       </c>
-      <c r="AP50" s="92"/>
+      <c r="AP50" s="90"/>
     </row>
     <row r="51" spans="13:42" x14ac:dyDescent="0.25">
       <c r="Y51" s="84"/>
@@ -18140,10 +18155,10 @@
       <c r="AI51" s="74"/>
       <c r="AJ51" s="74"/>
       <c r="AK51" s="74"/>
-      <c r="AM51" s="92" t="s">
+      <c r="AM51" s="90" t="s">
         <v>383</v>
       </c>
-      <c r="AP51" s="92"/>
+      <c r="AP51" s="90"/>
     </row>
     <row r="52" spans="13:42" x14ac:dyDescent="0.25">
       <c r="Z52" s="84"/>
@@ -18158,10 +18173,10 @@
       <c r="AJ52" s="74"/>
       <c r="AK52" s="74"/>
       <c r="AL52" s="74"/>
-      <c r="AM52" s="92" t="s">
+      <c r="AM52" s="90" t="s">
         <v>382</v>
       </c>
-      <c r="AP52" s="92"/>
+      <c r="AP52" s="90"/>
     </row>
     <row r="53" spans="13:42" x14ac:dyDescent="0.25">
       <c r="AA53" s="84"/>
@@ -18175,13 +18190,13 @@
       <c r="AJ53" s="74"/>
       <c r="AK53" s="74"/>
       <c r="AL53" s="74"/>
-      <c r="AM53" s="92" t="s">
+      <c r="AM53" s="90" t="s">
         <v>382</v>
       </c>
-      <c r="AP53" s="92"/>
+      <c r="AP53" s="90"/>
     </row>
     <row r="54" spans="13:42" x14ac:dyDescent="0.25">
-      <c r="W54" s="95" t="s">
+      <c r="W54" s="93" t="s">
         <v>391</v>
       </c>
       <c r="X54" s="71"/>
@@ -18189,7 +18204,7 @@
       <c r="Z54" s="71"/>
       <c r="AA54" s="71"/>
       <c r="AB54" s="78"/>
-      <c r="AP54" s="92"/>
+      <c r="AP54" s="90"/>
     </row>
     <row r="55" spans="13:42" x14ac:dyDescent="0.25">
       <c r="AC55" s="70"/>
@@ -18198,7 +18213,7 @@
       <c r="AG55" s="71"/>
       <c r="AH55" s="71"/>
       <c r="AI55" s="71"/>
-      <c r="AK55" s="92" t="s">
+      <c r="AK55" s="90" t="s">
         <v>385</v>
       </c>
     </row>
@@ -18214,7 +18229,7 @@
       <c r="AI56" s="71"/>
       <c r="AJ56" s="75"/>
       <c r="AK56" s="71"/>
-      <c r="AL56" s="92" t="s">
+      <c r="AL56" s="90" t="s">
         <v>390</v>
       </c>
     </row>
@@ -18222,14 +18237,14 @@
   <mergeCells count="42">
     <mergeCell ref="BR20:BS20"/>
     <mergeCell ref="L20:M20"/>
-    <mergeCell ref="BO36:BR36"/>
+    <mergeCell ref="BQ36:BT36"/>
     <mergeCell ref="AB35:AE35"/>
     <mergeCell ref="AB36:AE36"/>
     <mergeCell ref="M49:N49"/>
     <mergeCell ref="O1:R1"/>
     <mergeCell ref="N2:S2"/>
     <mergeCell ref="M48:N48"/>
-    <mergeCell ref="BO37:BR37"/>
+    <mergeCell ref="BQ37:BT37"/>
     <mergeCell ref="AE12:AF12"/>
     <mergeCell ref="AQ11:AR11"/>
     <mergeCell ref="BH11:BK11"/>
@@ -18251,9 +18266,9 @@
     <mergeCell ref="CA19:CB19"/>
     <mergeCell ref="O31:P31"/>
     <mergeCell ref="Z31:AA31"/>
-    <mergeCell ref="AK30:AL30"/>
-    <mergeCell ref="AV30:AW30"/>
-    <mergeCell ref="BJ30:BK30"/>
+    <mergeCell ref="AM30:AN30"/>
+    <mergeCell ref="AX30:AY30"/>
+    <mergeCell ref="BM30:BN30"/>
     <mergeCell ref="BZ20:CC20"/>
     <mergeCell ref="AI21:AJ21"/>
     <mergeCell ref="W20:X20"/>
@@ -18265,12 +18280,13 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F50BE23F-6E19-4986-A071-1BA966419E21}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="F2:BZ34"/>
   <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -18309,7 +18325,7 @@
     <row r="8" spans="6:77" x14ac:dyDescent="0.25">
       <c r="H8" s="58"/>
       <c r="I8" s="57"/>
-      <c r="J8" s="99">
+      <c r="J8" s="97">
         <v>5</v>
       </c>
       <c r="K8" s="58"/>
@@ -18326,21 +18342,21 @@
       <c r="AG8" s="63"/>
     </row>
     <row r="9" spans="6:77" x14ac:dyDescent="0.25">
-      <c r="F9" s="96">
+      <c r="F9" s="94">
         <v>1</v>
       </c>
       <c r="G9" s="57"/>
-      <c r="H9" s="97">
+      <c r="H9" s="95">
         <v>2</v>
       </c>
-      <c r="I9" s="96">
+      <c r="I9" s="94">
         <v>4</v>
       </c>
       <c r="J9" s="28"/>
-      <c r="K9" s="100">
+      <c r="K9" s="98">
         <v>6</v>
       </c>
-      <c r="L9" s="118">
+      <c r="L9" s="116">
         <v>8</v>
       </c>
       <c r="N9" s="51" t="s">
@@ -18355,15 +18371,15 @@
     </row>
     <row r="10" spans="6:77" x14ac:dyDescent="0.25">
       <c r="F10" s="27"/>
-      <c r="H10" s="98">
+      <c r="H10" s="96">
         <v>3</v>
       </c>
       <c r="I10" s="27"/>
       <c r="J10" s="27"/>
-      <c r="K10" s="101" t="s">
+      <c r="K10" s="99" t="s">
         <v>434</v>
       </c>
-      <c r="L10" s="102">
+      <c r="L10" s="100">
         <v>9</v>
       </c>
       <c r="N10" s="51" t="s">
@@ -18380,7 +18396,7 @@
       <c r="BJ10" s="16"/>
       <c r="BK10" s="16"/>
       <c r="BL10" s="16"/>
-      <c r="BM10" s="105">
+      <c r="BM10" s="103">
         <v>1</v>
       </c>
     </row>
@@ -18411,7 +18427,7 @@
       <c r="AC11" s="16"/>
       <c r="AD11" s="16"/>
       <c r="AE11" s="16"/>
-      <c r="AF11" s="103">
+      <c r="AF11" s="101">
         <v>1</v>
       </c>
       <c r="AG11" s="16"/>
@@ -18437,7 +18453,7 @@
       <c r="BA11" s="16"/>
       <c r="BB11" s="16"/>
       <c r="BC11" s="16"/>
-      <c r="BD11" s="103">
+      <c r="BD11" s="101">
         <v>1</v>
       </c>
       <c r="BE11" s="16"/>
@@ -18457,7 +18473,7 @@
       <c r="BS11" s="16"/>
       <c r="BT11" s="16"/>
       <c r="BU11" s="16"/>
-      <c r="BV11" s="103">
+      <c r="BV11" s="101">
         <v>1</v>
       </c>
       <c r="BW11" s="16"/>
@@ -18556,10 +18572,10 @@
       <c r="V13" s="21"/>
       <c r="X13" s="21"/>
       <c r="Y13" s="21"/>
-      <c r="AN13" s="104">
+      <c r="AN13" s="102">
         <v>1</v>
       </c>
-      <c r="AV13" s="104">
+      <c r="AV13" s="102">
         <v>1</v>
       </c>
       <c r="BH13" s="25"/>
@@ -18587,32 +18603,32 @@
       <c r="U14" s="21"/>
       <c r="W14" s="19"/>
       <c r="X14" s="19"/>
-      <c r="AC14" s="126" t="s">
+      <c r="AC14" s="129" t="s">
         <v>60</v>
       </c>
-      <c r="AD14" s="126"/>
-      <c r="AK14" s="126" t="s">
+      <c r="AD14" s="129"/>
+      <c r="AK14" s="129" t="s">
         <v>61</v>
       </c>
-      <c r="AL14" s="126"/>
-      <c r="AS14" s="126" t="s">
+      <c r="AL14" s="129"/>
+      <c r="AS14" s="129" t="s">
         <v>397</v>
       </c>
-      <c r="AT14" s="126"/>
-      <c r="AZ14" s="126" t="s">
+      <c r="AT14" s="129"/>
+      <c r="AZ14" s="129" t="s">
         <v>399</v>
       </c>
-      <c r="BA14" s="126"/>
-      <c r="BB14" s="126"/>
-      <c r="BC14" s="126"/>
-      <c r="BJ14" s="127" t="s">
+      <c r="BA14" s="129"/>
+      <c r="BB14" s="129"/>
+      <c r="BC14" s="129"/>
+      <c r="BJ14" s="130" t="s">
         <v>64</v>
       </c>
-      <c r="BK14" s="127"/>
-      <c r="BS14" s="126" t="s">
+      <c r="BK14" s="130"/>
+      <c r="BS14" s="129" t="s">
         <v>65</v>
       </c>
-      <c r="BT14" s="126"/>
+      <c r="BT14" s="129"/>
     </row>
     <row r="15" spans="6:77" x14ac:dyDescent="0.25">
       <c r="H15" s="55"/>
@@ -18631,44 +18647,44 @@
       <c r="T15" s="21"/>
       <c r="V15" s="19"/>
       <c r="W15" s="19"/>
-      <c r="AB15" s="126" t="s">
+      <c r="AB15" s="129" t="s">
         <v>393</v>
       </c>
-      <c r="AC15" s="126"/>
-      <c r="AD15" s="126"/>
-      <c r="AE15" s="126"/>
-      <c r="AJ15" s="126" t="s">
+      <c r="AC15" s="129"/>
+      <c r="AD15" s="129"/>
+      <c r="AE15" s="129"/>
+      <c r="AJ15" s="129" t="s">
         <v>396</v>
       </c>
-      <c r="AK15" s="126"/>
-      <c r="AL15" s="126"/>
-      <c r="AM15" s="126"/>
-      <c r="AR15" s="126" t="s">
+      <c r="AK15" s="129"/>
+      <c r="AL15" s="129"/>
+      <c r="AM15" s="129"/>
+      <c r="AR15" s="129" t="s">
         <v>398</v>
       </c>
-      <c r="AS15" s="126"/>
-      <c r="AT15" s="126"/>
-      <c r="AU15" s="126"/>
-      <c r="AY15" s="126" t="s">
+      <c r="AS15" s="129"/>
+      <c r="AT15" s="129"/>
+      <c r="AU15" s="129"/>
+      <c r="AY15" s="129" t="s">
         <v>400</v>
       </c>
-      <c r="AZ15" s="126"/>
-      <c r="BA15" s="126"/>
-      <c r="BB15" s="126"/>
-      <c r="BC15" s="126"/>
-      <c r="BD15" s="126"/>
-      <c r="BI15" s="126" t="s">
+      <c r="AZ15" s="129"/>
+      <c r="BA15" s="129"/>
+      <c r="BB15" s="129"/>
+      <c r="BC15" s="129"/>
+      <c r="BD15" s="129"/>
+      <c r="BI15" s="129" t="s">
         <v>401</v>
       </c>
-      <c r="BJ15" s="126"/>
-      <c r="BK15" s="126"/>
-      <c r="BL15" s="126"/>
-      <c r="BR15" s="126" t="s">
+      <c r="BJ15" s="129"/>
+      <c r="BK15" s="129"/>
+      <c r="BL15" s="129"/>
+      <c r="BR15" s="129" t="s">
         <v>402</v>
       </c>
-      <c r="BS15" s="126"/>
-      <c r="BT15" s="126"/>
-      <c r="BU15" s="126"/>
+      <c r="BS15" s="129"/>
+      <c r="BT15" s="129"/>
+      <c r="BU15" s="129"/>
     </row>
     <row r="16" spans="6:77" x14ac:dyDescent="0.4">
       <c r="H16" s="28"/>
@@ -18681,7 +18697,7 @@
     <row r="17" spans="8:78" x14ac:dyDescent="0.4">
       <c r="H17" s="28"/>
       <c r="J17" s="28"/>
-      <c r="K17" s="119"/>
+      <c r="K17" s="117"/>
       <c r="L17" s="52"/>
       <c r="O17" t="s">
         <v>395</v>
@@ -18693,7 +18709,7 @@
       <c r="H18" s="28"/>
       <c r="I18" s="19"/>
       <c r="K18" s="18"/>
-      <c r="L18" s="119"/>
+      <c r="L18" s="117"/>
       <c r="M18" s="28"/>
       <c r="S18" s="19"/>
       <c r="T18" s="19"/>
@@ -18723,23 +18739,23 @@
     <row r="21" spans="8:78" x14ac:dyDescent="0.4">
       <c r="H21" s="28"/>
       <c r="I21" s="28"/>
-      <c r="L21" s="126" t="s">
+      <c r="L21" s="129" t="s">
         <v>394</v>
       </c>
-      <c r="M21" s="126"/>
+      <c r="M21" s="129"/>
     </row>
     <row r="22" spans="8:78" x14ac:dyDescent="0.4">
-      <c r="L22" s="126" t="s">
+      <c r="L22" s="129" t="s">
         <v>187</v>
       </c>
-      <c r="M22" s="126"/>
+      <c r="M22" s="129"/>
     </row>
     <row r="24" spans="8:78" x14ac:dyDescent="0.25">
       <c r="W24" s="16"/>
       <c r="X24" s="16"/>
       <c r="Y24" s="16"/>
       <c r="Z24" s="16"/>
-      <c r="AB24" s="105">
+      <c r="AB24" s="103">
         <v>1</v>
       </c>
     </row>
@@ -18764,7 +18780,7 @@
       <c r="AG25" s="16"/>
       <c r="AH25" s="16"/>
       <c r="AI25" s="16"/>
-      <c r="AJ25" s="107">
+      <c r="AJ25" s="105">
         <v>2</v>
       </c>
       <c r="AK25" s="16"/>
@@ -18788,7 +18804,7 @@
       <c r="BC25" s="16"/>
       <c r="BD25" s="16"/>
       <c r="BE25" s="16"/>
-      <c r="BF25" s="103">
+      <c r="BF25" s="101">
         <v>1</v>
       </c>
       <c r="BG25" s="16"/>
@@ -18798,7 +18814,7 @@
       <c r="BK25" s="16"/>
       <c r="BL25" s="16"/>
       <c r="BM25" s="16"/>
-      <c r="BN25" s="103">
+      <c r="BN25" s="101">
         <v>1</v>
       </c>
       <c r="BO25" s="16"/>
@@ -18833,7 +18849,7 @@
       <c r="AG26" s="16"/>
       <c r="AH26" s="23"/>
       <c r="AI26" s="16"/>
-      <c r="AJ26" s="107">
+      <c r="AJ26" s="105">
         <v>1</v>
       </c>
       <c r="AK26" s="16"/>
@@ -18891,13 +18907,13 @@
       <c r="AM27" s="16"/>
       <c r="AN27" s="16"/>
       <c r="AO27" s="22"/>
-      <c r="AX27" s="104">
+      <c r="AX27" s="102">
         <v>1</v>
       </c>
-      <c r="BK27" s="126" t="s">
+      <c r="BK27" s="129" t="s">
         <v>637</v>
       </c>
-      <c r="BL27" s="126"/>
+      <c r="BL27" s="129"/>
       <c r="BT27" s="25"/>
       <c r="BU27" s="17"/>
       <c r="BV27" s="17"/>
@@ -18906,74 +18922,74 @@
       <c r="BY27" s="17"/>
     </row>
     <row r="28" spans="8:78" x14ac:dyDescent="0.4">
-      <c r="X28" s="127" t="s">
+      <c r="X28" s="130" t="s">
         <v>66</v>
       </c>
-      <c r="Y28" s="127"/>
-      <c r="AJ28" s="106">
+      <c r="Y28" s="130"/>
+      <c r="AJ28" s="104">
         <v>0</v>
       </c>
-      <c r="AK28" s="127" t="s">
+      <c r="AK28" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="AL28" s="127"/>
-      <c r="AM28" s="127"/>
-      <c r="AN28" s="127"/>
+      <c r="AL28" s="130"/>
+      <c r="AM28" s="130"/>
+      <c r="AN28" s="130"/>
       <c r="AP28" s="18"/>
-      <c r="AU28" s="126" t="s">
+      <c r="AU28" s="129" t="s">
         <v>68</v>
       </c>
-      <c r="AV28" s="126"/>
-      <c r="BC28" s="126" t="s">
+      <c r="AV28" s="129"/>
+      <c r="BC28" s="129" t="s">
         <v>69</v>
       </c>
-      <c r="BD28" s="126"/>
-      <c r="BJ28" s="126" t="s">
+      <c r="BD28" s="129"/>
+      <c r="BJ28" s="129" t="s">
         <v>638</v>
       </c>
-      <c r="BK28" s="126"/>
-      <c r="BL28" s="126"/>
-      <c r="BM28" s="126"/>
-      <c r="BW28" s="126" t="s">
+      <c r="BK28" s="129"/>
+      <c r="BL28" s="129"/>
+      <c r="BM28" s="129"/>
+      <c r="BW28" s="129" t="s">
         <v>639</v>
       </c>
-      <c r="BX28" s="126"/>
-      <c r="BZ28" s="104">
+      <c r="BX28" s="129"/>
+      <c r="BZ28" s="102">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="8:78" x14ac:dyDescent="0.4">
-      <c r="W29" s="126" t="s">
+      <c r="W29" s="129" t="s">
         <v>403</v>
       </c>
-      <c r="X29" s="126"/>
-      <c r="Y29" s="126"/>
-      <c r="Z29" s="126"/>
-      <c r="AK29" s="126" t="s">
+      <c r="X29" s="129"/>
+      <c r="Y29" s="129"/>
+      <c r="Z29" s="129"/>
+      <c r="AK29" s="129" t="s">
         <v>405</v>
       </c>
-      <c r="AL29" s="126"/>
-      <c r="AM29" s="126"/>
-      <c r="AN29" s="126"/>
+      <c r="AL29" s="129"/>
+      <c r="AM29" s="129"/>
+      <c r="AN29" s="129"/>
       <c r="AQ29" s="18"/>
-      <c r="AS29" s="126" t="s">
+      <c r="AS29" s="129" t="s">
         <v>406</v>
       </c>
-      <c r="AT29" s="126"/>
-      <c r="AU29" s="126"/>
-      <c r="AV29" s="126"/>
-      <c r="AW29" s="126"/>
-      <c r="AX29" s="126"/>
-      <c r="BC29" s="126" t="s">
+      <c r="AT29" s="129"/>
+      <c r="AU29" s="129"/>
+      <c r="AV29" s="129"/>
+      <c r="AW29" s="129"/>
+      <c r="AX29" s="129"/>
+      <c r="BC29" s="129" t="s">
         <v>407</v>
       </c>
-      <c r="BD29" s="126"/>
-      <c r="BV29" s="126" t="s">
+      <c r="BD29" s="129"/>
+      <c r="BV29" s="129" t="s">
         <v>640</v>
       </c>
-      <c r="BW29" s="126"/>
-      <c r="BX29" s="126"/>
-      <c r="BY29" s="126"/>
+      <c r="BW29" s="129"/>
+      <c r="BX29" s="129"/>
+      <c r="BY29" s="129"/>
     </row>
     <row r="30" spans="8:78" x14ac:dyDescent="0.4">
       <c r="AP30" t="s">
@@ -18996,16 +19012,16 @@
       <c r="BA31" s="16"/>
     </row>
     <row r="33" spans="51:52" x14ac:dyDescent="0.4">
-      <c r="AY33" s="126" t="s">
+      <c r="AY33" s="129" t="s">
         <v>118</v>
       </c>
-      <c r="AZ33" s="126"/>
+      <c r="AZ33" s="129"/>
     </row>
     <row r="34" spans="51:52" x14ac:dyDescent="0.4">
-      <c r="AY34" s="126" t="s">
+      <c r="AY34" s="129" t="s">
         <v>404</v>
       </c>
-      <c r="AZ34" s="126"/>
+      <c r="AZ34" s="129"/>
     </row>
   </sheetData>
   <mergeCells count="28">
@@ -19045,7 +19061,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AF97548-0F5A-4933-8441-4342220A91AD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="E3:CB19"/>
   <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -19054,7 +19070,7 @@
       <c r="F3" s="16"/>
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
-      <c r="I3" s="105">
+      <c r="I3" s="103">
         <v>1</v>
       </c>
       <c r="N3" s="16"/>
@@ -19114,7 +19130,7 @@
       <c r="AB4" s="16"/>
       <c r="AC4" s="16"/>
       <c r="AD4" s="16"/>
-      <c r="AE4" s="103">
+      <c r="AE4" s="101">
         <v>1</v>
       </c>
       <c r="AF4" s="16"/>
@@ -19124,7 +19140,7 @@
       <c r="AJ4" s="16"/>
       <c r="AK4" s="16"/>
       <c r="AL4" s="16"/>
-      <c r="AM4" s="103">
+      <c r="AM4" s="101">
         <v>1</v>
       </c>
       <c r="AN4" s="16"/>
@@ -19148,7 +19164,7 @@
       <c r="BF4" s="16"/>
       <c r="BG4" s="16"/>
       <c r="BH4" s="16"/>
-      <c r="BI4" s="103">
+      <c r="BI4" s="101">
         <v>1</v>
       </c>
       <c r="BJ4" s="16"/>
@@ -19162,7 +19178,7 @@
       <c r="BR4" s="16"/>
       <c r="BS4" s="16"/>
       <c r="BT4" s="16"/>
-      <c r="BU4" s="103">
+      <c r="BU4" s="101">
         <v>1</v>
       </c>
       <c r="BV4" s="16"/>
@@ -19274,76 +19290,76 @@
       <c r="BX6" s="19"/>
     </row>
     <row r="7" spans="5:80" x14ac:dyDescent="0.4">
-      <c r="F7" s="126" t="s">
+      <c r="F7" s="129" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="126"/>
-      <c r="AB7" s="126" t="s">
+      <c r="G7" s="129"/>
+      <c r="AB7" s="129" t="s">
         <v>416</v>
       </c>
-      <c r="AC7" s="126"/>
-      <c r="AJ7" s="126" t="s">
+      <c r="AC7" s="129"/>
+      <c r="AJ7" s="129" t="s">
         <v>40</v>
       </c>
-      <c r="AK7" s="126"/>
-      <c r="AU7" s="127" t="s">
+      <c r="AK7" s="129"/>
+      <c r="AU7" s="130" t="s">
         <v>41</v>
       </c>
-      <c r="AV7" s="127"/>
-      <c r="AX7" s="104">
+      <c r="AV7" s="130"/>
+      <c r="AX7" s="102">
         <v>1</v>
       </c>
-      <c r="BF7" s="126" t="s">
+      <c r="BF7" s="129" t="s">
         <v>420</v>
       </c>
-      <c r="BG7" s="126"/>
-      <c r="BR7" s="126" t="s">
+      <c r="BG7" s="129"/>
+      <c r="BR7" s="129" t="s">
         <v>43</v>
       </c>
-      <c r="BS7" s="126"/>
+      <c r="BS7" s="129"/>
     </row>
     <row r="8" spans="5:80" x14ac:dyDescent="0.4">
-      <c r="E8" s="126" t="s">
+      <c r="E8" s="129" t="s">
         <v>415</v>
       </c>
-      <c r="F8" s="126"/>
-      <c r="G8" s="126"/>
-      <c r="H8" s="126"/>
-      <c r="Q8" s="126" t="s">
+      <c r="F8" s="129"/>
+      <c r="G8" s="129"/>
+      <c r="H8" s="129"/>
+      <c r="Q8" s="129" t="s">
         <v>414</v>
       </c>
-      <c r="R8" s="126"/>
-      <c r="S8" s="126"/>
-      <c r="T8" s="126"/>
-      <c r="U8" s="126"/>
-      <c r="AB8" s="126" t="s">
+      <c r="R8" s="129"/>
+      <c r="S8" s="129"/>
+      <c r="T8" s="129"/>
+      <c r="U8" s="129"/>
+      <c r="AB8" s="129" t="s">
         <v>417</v>
       </c>
-      <c r="AC8" s="126"/>
-      <c r="AI8" s="126" t="s">
+      <c r="AC8" s="129"/>
+      <c r="AI8" s="129" t="s">
         <v>418</v>
       </c>
-      <c r="AJ8" s="126"/>
-      <c r="AK8" s="126"/>
-      <c r="AL8" s="126"/>
-      <c r="AT8" s="126" t="s">
+      <c r="AJ8" s="129"/>
+      <c r="AK8" s="129"/>
+      <c r="AL8" s="129"/>
+      <c r="AT8" s="129" t="s">
         <v>419</v>
       </c>
-      <c r="AU8" s="126"/>
-      <c r="AV8" s="126"/>
-      <c r="AW8" s="126"/>
-      <c r="BE8" s="126" t="s">
+      <c r="AU8" s="129"/>
+      <c r="AV8" s="129"/>
+      <c r="AW8" s="129"/>
+      <c r="BE8" s="129" t="s">
         <v>421</v>
       </c>
-      <c r="BF8" s="126"/>
-      <c r="BG8" s="126"/>
-      <c r="BH8" s="126"/>
-      <c r="BQ8" s="126" t="s">
+      <c r="BF8" s="129"/>
+      <c r="BG8" s="129"/>
+      <c r="BH8" s="129"/>
+      <c r="BQ8" s="129" t="s">
         <v>422</v>
       </c>
-      <c r="BR8" s="126"/>
-      <c r="BS8" s="126"/>
-      <c r="BT8" s="126"/>
+      <c r="BR8" s="129"/>
+      <c r="BS8" s="129"/>
+      <c r="BT8" s="129"/>
     </row>
     <row r="11" spans="5:80" x14ac:dyDescent="0.25">
       <c r="N11" t="s">
@@ -19356,7 +19372,7 @@
       <c r="AC11" s="16"/>
       <c r="AD11" s="16"/>
       <c r="AE11" s="16"/>
-      <c r="AF11" s="105">
+      <c r="AF11" s="103">
         <v>0</v>
       </c>
       <c r="AH11" t="s">
@@ -19402,7 +19418,7 @@
       <c r="AC12" s="16"/>
       <c r="AD12" s="16"/>
       <c r="AE12" s="16"/>
-      <c r="AF12" s="108">
+      <c r="AF12" s="106">
         <v>1</v>
       </c>
       <c r="AG12" s="16"/>
@@ -19423,7 +19439,7 @@
       <c r="AV12" s="16"/>
       <c r="AW12" s="16"/>
       <c r="AX12" s="16"/>
-      <c r="AY12" s="103">
+      <c r="AY12" s="101">
         <v>1</v>
       </c>
       <c r="AZ12" s="16"/>
@@ -19516,13 +19532,13 @@
       <c r="BY13" s="16"/>
     </row>
     <row r="14" spans="5:80" x14ac:dyDescent="0.4">
-      <c r="M14" s="104">
+      <c r="M14" s="102">
         <v>1</v>
       </c>
-      <c r="V14" s="104">
+      <c r="V14" s="102">
         <v>1</v>
       </c>
-      <c r="AF14" s="104">
+      <c r="AF14" s="102">
         <v>2</v>
       </c>
       <c r="AK14" s="25"/>
@@ -19555,29 +19571,29 @@
       <c r="BY14" s="17"/>
     </row>
     <row r="15" spans="5:80" x14ac:dyDescent="0.4">
-      <c r="J15" s="126" t="s">
+      <c r="J15" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="K15" s="126"/>
-      <c r="S15" s="126" t="s">
+      <c r="K15" s="129"/>
+      <c r="S15" s="129" t="s">
         <v>51</v>
       </c>
-      <c r="T15" s="126"/>
-      <c r="AC15" s="126" t="s">
+      <c r="T15" s="129"/>
+      <c r="AC15" s="129" t="s">
         <v>424</v>
       </c>
-      <c r="AD15" s="126"/>
-      <c r="AM15" s="126" t="s">
+      <c r="AD15" s="129"/>
+      <c r="AM15" s="129" t="s">
         <v>55</v>
       </c>
-      <c r="AN15" s="126"/>
-      <c r="AP15" s="104">
+      <c r="AN15" s="129"/>
+      <c r="AP15" s="102">
         <v>1</v>
       </c>
-      <c r="AV15" s="126" t="s">
+      <c r="AV15" s="129" t="s">
         <v>427</v>
       </c>
-      <c r="AW15" s="126"/>
+      <c r="AW15" s="129"/>
       <c r="BC15" s="19"/>
       <c r="BD15" s="67"/>
       <c r="BE15" s="66"/>
@@ -19591,30 +19607,30 @@
       <c r="BS15" s="19"/>
     </row>
     <row r="16" spans="5:80" x14ac:dyDescent="0.4">
-      <c r="J16" s="126" t="s">
+      <c r="J16" s="129" t="s">
         <v>553</v>
       </c>
-      <c r="K16" s="126"/>
-      <c r="S16" s="126" t="s">
+      <c r="K16" s="129"/>
+      <c r="S16" s="129" t="s">
         <v>423</v>
       </c>
-      <c r="T16" s="126"/>
-      <c r="AB16" s="126" t="s">
+      <c r="T16" s="129"/>
+      <c r="AB16" s="129" t="s">
         <v>425</v>
       </c>
-      <c r="AC16" s="126"/>
-      <c r="AD16" s="126"/>
-      <c r="AE16" s="126"/>
-      <c r="AM16" s="126" t="s">
+      <c r="AC16" s="129"/>
+      <c r="AD16" s="129"/>
+      <c r="AE16" s="129"/>
+      <c r="AM16" s="129" t="s">
         <v>426</v>
       </c>
-      <c r="AN16" s="126"/>
-      <c r="AU16" s="126" t="s">
+      <c r="AN16" s="129"/>
+      <c r="AU16" s="129" t="s">
         <v>428</v>
       </c>
-      <c r="AV16" s="126"/>
-      <c r="AW16" s="126"/>
-      <c r="AX16" s="126"/>
+      <c r="AV16" s="129"/>
+      <c r="AW16" s="129"/>
+      <c r="AX16" s="129"/>
       <c r="BB16" s="19"/>
       <c r="BD16" s="19"/>
       <c r="BM16" s="18"/>
@@ -19627,10 +19643,10 @@
     <row r="17" spans="52:70" x14ac:dyDescent="0.4">
       <c r="BA17" s="19"/>
       <c r="BC17" s="19"/>
-      <c r="BO17" s="126" t="s">
+      <c r="BO17" s="129" t="s">
         <v>2</v>
       </c>
-      <c r="BP17" s="126"/>
+      <c r="BP17" s="129"/>
       <c r="BR17" t="s">
         <v>178</v>
       </c>
@@ -19639,10 +19655,10 @@
       <c r="AZ18" t="s">
         <v>429</v>
       </c>
-      <c r="BO18" s="126" t="s">
+      <c r="BO18" s="129" t="s">
         <v>185</v>
       </c>
-      <c r="BP18" s="126"/>
+      <c r="BP18" s="129"/>
     </row>
     <row r="19" spans="52:70" x14ac:dyDescent="0.4">
       <c r="AZ19" t="s">
@@ -19684,7 +19700,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{311108F8-D62A-4598-A852-EAC8B0202FB3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:BO84"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
@@ -19797,7 +19813,7 @@
       <c r="BK2" s="28"/>
     </row>
     <row r="3" spans="2:67" x14ac:dyDescent="0.4">
-      <c r="N3" s="121" t="s">
+      <c r="N3" s="119" t="s">
         <v>686</v>
       </c>
       <c r="AK3" s="34" t="s">
@@ -19806,7 +19822,7 @@
       <c r="AL3">
         <v>0</v>
       </c>
-      <c r="AM3" s="129">
+      <c r="AM3" s="132">
         <v>1991</v>
       </c>
       <c r="AN3" s="28">
@@ -19841,7 +19857,7 @@
       <c r="AL4">
         <v>0</v>
       </c>
-      <c r="AM4" s="128"/>
+      <c r="AM4" s="131"/>
       <c r="AN4" s="28">
         <v>9</v>
       </c>
@@ -19972,7 +19988,7 @@
       <c r="AL6">
         <v>1</v>
       </c>
-      <c r="AM6" s="129">
+      <c r="AM6" s="132">
         <v>1995</v>
       </c>
       <c r="AN6" s="28"/>
@@ -20031,7 +20047,7 @@
       <c r="AL7">
         <v>1</v>
       </c>
-      <c r="AM7" s="128"/>
+      <c r="AM7" s="131"/>
       <c r="AN7" s="28"/>
       <c r="AO7" s="28">
         <v>2</v>
@@ -20085,7 +20101,7 @@
       <c r="AL8">
         <v>1</v>
       </c>
-      <c r="AM8" s="128"/>
+      <c r="AM8" s="131"/>
       <c r="AN8" s="28"/>
       <c r="AO8" s="28">
         <v>3</v>
@@ -20137,7 +20153,7 @@
       <c r="AL9">
         <v>1</v>
       </c>
-      <c r="AM9" s="128"/>
+      <c r="AM9" s="131"/>
       <c r="AN9" s="28"/>
       <c r="AO9" s="28">
         <v>4</v>
@@ -20188,7 +20204,7 @@
       <c r="AL10">
         <v>2</v>
       </c>
-      <c r="AM10" s="128"/>
+      <c r="AM10" s="131"/>
       <c r="AN10" s="28"/>
       <c r="AO10" s="28">
         <v>5</v>
@@ -20233,7 +20249,7 @@
       <c r="AL11">
         <v>3</v>
       </c>
-      <c r="AM11" s="128"/>
+      <c r="AM11" s="131"/>
       <c r="AN11" s="28"/>
       <c r="AO11" s="28">
         <v>6</v>
@@ -20306,7 +20322,7 @@
       <c r="AL12">
         <v>3</v>
       </c>
-      <c r="AM12" s="128"/>
+      <c r="AM12" s="131"/>
       <c r="AN12" s="28"/>
       <c r="AO12" s="28">
         <v>7</v>
@@ -20358,7 +20374,7 @@
       <c r="AL13">
         <v>3</v>
       </c>
-      <c r="AM13" s="128"/>
+      <c r="AM13" s="131"/>
       <c r="AN13" s="28"/>
       <c r="AO13" s="28">
         <v>8</v>
@@ -20394,7 +20410,7 @@
       <c r="H14" s="34" t="s">
         <v>214</v>
       </c>
-      <c r="N14" s="130" t="s">
+      <c r="N14" s="133" t="s">
         <v>366</v>
       </c>
       <c r="O14" s="34" t="s">
@@ -20403,7 +20419,7 @@
       <c r="P14" s="34" t="s">
         <v>357</v>
       </c>
-      <c r="Q14" s="130" t="s">
+      <c r="Q14" s="133" t="s">
         <v>459</v>
       </c>
       <c r="R14" s="34"/>
@@ -20422,7 +20438,7 @@
       <c r="AL14">
         <v>2</v>
       </c>
-      <c r="AM14" s="128"/>
+      <c r="AM14" s="131"/>
       <c r="AN14" s="28"/>
       <c r="AO14" s="28">
         <v>9</v>
@@ -20446,8 +20462,8 @@
       <c r="G15" t="s">
         <v>216</v>
       </c>
-      <c r="N15" s="130"/>
-      <c r="Q15" s="131"/>
+      <c r="N15" s="133"/>
+      <c r="Q15" s="134"/>
       <c r="AJ15">
         <v>10</v>
       </c>
@@ -20457,7 +20473,7 @@
       <c r="AL15">
         <v>2</v>
       </c>
-      <c r="AM15" s="128">
+      <c r="AM15" s="131">
         <v>1996</v>
       </c>
       <c r="AN15" s="28"/>
@@ -20498,7 +20514,7 @@
       <c r="AL16">
         <v>2</v>
       </c>
-      <c r="AM16" s="128"/>
+      <c r="AM16" s="131"/>
       <c r="AN16" s="28"/>
       <c r="AO16" s="28">
         <v>11</v>
@@ -20525,7 +20541,7 @@
       <c r="AL17">
         <v>2</v>
       </c>
-      <c r="AM17" s="128"/>
+      <c r="AM17" s="131"/>
       <c r="AN17" s="28"/>
       <c r="AO17" s="28">
         <v>12</v>
@@ -20558,7 +20574,7 @@
       <c r="AL18">
         <v>2</v>
       </c>
-      <c r="AM18" s="128"/>
+      <c r="AM18" s="131"/>
       <c r="AN18" s="28"/>
       <c r="AO18" s="28">
         <v>13</v>
@@ -20613,7 +20629,7 @@
       <c r="AL19">
         <v>3</v>
       </c>
-      <c r="AM19" s="128">
+      <c r="AM19" s="131">
         <v>1997</v>
       </c>
       <c r="AN19" s="28"/>
@@ -20651,7 +20667,7 @@
       <c r="AL20">
         <v>3</v>
       </c>
-      <c r="AM20" s="128"/>
+      <c r="AM20" s="131"/>
       <c r="AN20" s="28"/>
       <c r="AO20" s="28">
         <v>15</v>
@@ -20688,7 +20704,7 @@
       <c r="AL21">
         <v>3</v>
       </c>
-      <c r="AM21" s="128"/>
+      <c r="AM21" s="131"/>
       <c r="AN21" s="28"/>
       <c r="AO21" s="28">
         <v>16</v>
@@ -20724,7 +20740,7 @@
       <c r="AL22">
         <v>3</v>
       </c>
-      <c r="AM22" s="128"/>
+      <c r="AM22" s="131"/>
       <c r="AN22" s="28"/>
       <c r="AO22" s="28">
         <v>17</v>
@@ -20748,7 +20764,7 @@
       <c r="AL23">
         <v>3</v>
       </c>
-      <c r="AM23" s="128"/>
+      <c r="AM23" s="131"/>
       <c r="AN23" s="28"/>
       <c r="AO23" s="28">
         <v>18</v>
@@ -20835,7 +20851,7 @@
       <c r="AL25">
         <v>2</v>
       </c>
-      <c r="AM25" s="128">
+      <c r="AM25" s="131">
         <v>1999</v>
       </c>
       <c r="AN25" s="28"/>
@@ -20876,7 +20892,7 @@
       <c r="AL26">
         <v>4</v>
       </c>
-      <c r="AM26" s="128"/>
+      <c r="AM26" s="131"/>
       <c r="AN26" s="28"/>
       <c r="AO26" s="28">
         <v>21</v>
@@ -20916,7 +20932,7 @@
       <c r="AL27">
         <v>4</v>
       </c>
-      <c r="AM27" s="128"/>
+      <c r="AM27" s="131"/>
       <c r="AN27" s="28"/>
       <c r="AO27" s="28">
         <v>22</v>
@@ -20955,7 +20971,7 @@
       <c r="AL28">
         <v>5</v>
       </c>
-      <c r="AM28" s="128"/>
+      <c r="AM28" s="131"/>
       <c r="AN28" s="28"/>
       <c r="AO28" s="28"/>
       <c r="BA28" s="28">
@@ -20982,7 +20998,7 @@
       <c r="AL29">
         <v>5</v>
       </c>
-      <c r="AM29" s="128"/>
+      <c r="AM29" s="131"/>
       <c r="AN29" s="28"/>
       <c r="AO29" s="28"/>
       <c r="BA29" s="28">
@@ -21015,7 +21031,7 @@
       <c r="AL30">
         <v>5</v>
       </c>
-      <c r="AM30" s="128"/>
+      <c r="AM30" s="131"/>
       <c r="AN30" s="28"/>
       <c r="AO30" s="28"/>
       <c r="BA30" s="28">
@@ -21067,7 +21083,7 @@
       <c r="AL31">
         <v>5</v>
       </c>
-      <c r="AM31" s="128"/>
+      <c r="AM31" s="131"/>
       <c r="AN31" s="28"/>
       <c r="AO31" s="28"/>
       <c r="BA31" s="28">
@@ -21103,7 +21119,7 @@
       <c r="AL32">
         <v>5</v>
       </c>
-      <c r="AM32" s="128"/>
+      <c r="AM32" s="131"/>
       <c r="AN32" s="28"/>
       <c r="AO32" s="28"/>
       <c r="BA32" s="28">
@@ -21141,7 +21157,7 @@
       <c r="AL33">
         <v>5</v>
       </c>
-      <c r="AM33" s="128"/>
+      <c r="AM33" s="131"/>
       <c r="AN33" s="28"/>
       <c r="AO33" s="28"/>
       <c r="BA33" s="28">
@@ -21177,7 +21193,7 @@
       <c r="AL34">
         <v>5</v>
       </c>
-      <c r="AM34" s="128"/>
+      <c r="AM34" s="131"/>
       <c r="AN34" s="28"/>
       <c r="AO34" s="28"/>
       <c r="BA34" s="28">
@@ -21204,7 +21220,7 @@
       <c r="AL35">
         <v>5</v>
       </c>
-      <c r="AM35" s="128"/>
+      <c r="AM35" s="131"/>
       <c r="AN35" s="28"/>
       <c r="AO35" s="28"/>
       <c r="BA35" s="28">
@@ -21237,7 +21253,7 @@
       <c r="AL36">
         <v>5</v>
       </c>
-      <c r="AM36" s="128"/>
+      <c r="AM36" s="131"/>
       <c r="AN36" s="28"/>
       <c r="AO36" s="28"/>
       <c r="BA36" s="28">
@@ -21294,7 +21310,7 @@
       <c r="AL37">
         <v>5</v>
       </c>
-      <c r="AM37" s="128"/>
+      <c r="AM37" s="131"/>
       <c r="AN37" s="28"/>
       <c r="AO37" s="28"/>
       <c r="BA37" s="28">
@@ -21333,7 +21349,7 @@
       <c r="AL38">
         <v>5</v>
       </c>
-      <c r="AM38" s="128"/>
+      <c r="AM38" s="131"/>
       <c r="AN38" s="28"/>
       <c r="AO38" s="28"/>
       <c r="BA38" s="28">
@@ -21351,10 +21367,10 @@
       <c r="BK38" s="28"/>
     </row>
     <row r="39" spans="12:63" x14ac:dyDescent="0.4">
-      <c r="N39" s="130" t="s">
+      <c r="N39" s="133" t="s">
         <v>445</v>
       </c>
-      <c r="O39" s="130" t="s">
+      <c r="O39" s="133" t="s">
         <v>371</v>
       </c>
       <c r="P39" s="34" t="s">
@@ -21375,7 +21391,7 @@
       <c r="AL39">
         <v>5</v>
       </c>
-      <c r="AM39" s="128"/>
+      <c r="AM39" s="131"/>
       <c r="AN39" s="28"/>
       <c r="AO39" s="28"/>
       <c r="BA39" s="28">
@@ -21393,8 +21409,8 @@
       <c r="BK39" s="28"/>
     </row>
     <row r="40" spans="12:63" x14ac:dyDescent="0.4">
-      <c r="N40" s="130"/>
-      <c r="O40" s="130"/>
+      <c r="N40" s="133"/>
+      <c r="O40" s="133"/>
       <c r="P40" s="34"/>
       <c r="Q40" s="34"/>
       <c r="R40" s="34"/>
@@ -21407,7 +21423,7 @@
       <c r="AL40">
         <v>4</v>
       </c>
-      <c r="AM40" s="128">
+      <c r="AM40" s="131">
         <v>2000</v>
       </c>
       <c r="AN40" s="28"/>
@@ -21451,7 +21467,7 @@
       <c r="AL41">
         <v>5</v>
       </c>
-      <c r="AM41" s="128"/>
+      <c r="AM41" s="131"/>
       <c r="AN41" s="28"/>
       <c r="AO41" s="28"/>
       <c r="BA41" s="28">
@@ -21478,7 +21494,7 @@
       <c r="AL42">
         <v>6</v>
       </c>
-      <c r="AM42" s="128"/>
+      <c r="AM42" s="131"/>
       <c r="AN42" s="28"/>
       <c r="AO42" s="28"/>
       <c r="BA42" s="28"/>
@@ -21503,7 +21519,7 @@
       <c r="AL43">
         <v>6</v>
       </c>
-      <c r="AM43" s="128"/>
+      <c r="AM43" s="131"/>
       <c r="AN43" s="28"/>
       <c r="AO43" s="28"/>
       <c r="BA43" s="28"/>
@@ -21534,7 +21550,7 @@
       <c r="AL44">
         <v>7</v>
       </c>
-      <c r="AM44" s="128"/>
+      <c r="AM44" s="131"/>
       <c r="AN44" s="28"/>
       <c r="AO44" s="28">
         <v>24</v>
@@ -21567,7 +21583,7 @@
       <c r="AL45">
         <v>7</v>
       </c>
-      <c r="AM45" s="128"/>
+      <c r="AM45" s="131"/>
       <c r="AN45" s="28"/>
       <c r="AO45" s="28">
         <v>25</v>
@@ -21622,7 +21638,7 @@
       <c r="AL46">
         <v>7</v>
       </c>
-      <c r="AM46" s="128"/>
+      <c r="AM46" s="131"/>
       <c r="AN46" s="28"/>
       <c r="AO46" s="28">
         <v>26</v>
@@ -21658,7 +21674,7 @@
       <c r="AL47">
         <v>7</v>
       </c>
-      <c r="AM47" s="128"/>
+      <c r="AM47" s="131"/>
       <c r="AN47" s="28"/>
       <c r="AO47" s="28">
         <v>27</v>
@@ -21698,7 +21714,7 @@
       <c r="AL48">
         <v>7</v>
       </c>
-      <c r="AM48" s="128"/>
+      <c r="AM48" s="131"/>
       <c r="AN48" s="28"/>
       <c r="AO48" s="28">
         <v>28</v>
@@ -21737,7 +21753,7 @@
       <c r="AL49">
         <v>8</v>
       </c>
-      <c r="AM49" s="128"/>
+      <c r="AM49" s="131"/>
       <c r="AN49" s="28"/>
       <c r="AO49" s="28">
         <v>29</v>
@@ -21761,7 +21777,7 @@
       <c r="AL50">
         <v>9</v>
       </c>
-      <c r="AM50" s="128">
+      <c r="AM50" s="131">
         <v>2001</v>
       </c>
       <c r="AN50" s="28"/>
@@ -21797,7 +21813,7 @@
       <c r="AL51">
         <v>9</v>
       </c>
-      <c r="AM51" s="128"/>
+      <c r="AM51" s="131"/>
       <c r="AN51" s="28"/>
       <c r="AO51" s="28"/>
       <c r="BA51" s="28">
@@ -21852,7 +21868,7 @@
       <c r="AL52">
         <v>9</v>
       </c>
-      <c r="AM52" s="128"/>
+      <c r="AM52" s="131"/>
       <c r="AN52" s="28"/>
       <c r="AO52" s="28"/>
       <c r="BA52" s="28">
@@ -21891,7 +21907,7 @@
       <c r="AL53">
         <v>9</v>
       </c>
-      <c r="AM53" s="128"/>
+      <c r="AM53" s="131"/>
       <c r="AN53" s="28"/>
       <c r="AO53" s="28"/>
       <c r="BA53" s="28">
@@ -21931,7 +21947,7 @@
       <c r="AL54">
         <v>9</v>
       </c>
-      <c r="AM54" s="128"/>
+      <c r="AM54" s="131"/>
       <c r="AN54" s="28"/>
       <c r="AO54" s="28"/>
       <c r="BA54" s="28">
@@ -21970,7 +21986,7 @@
       <c r="AL55">
         <v>9</v>
       </c>
-      <c r="AM55" s="128"/>
+      <c r="AM55" s="131"/>
       <c r="AN55" s="28"/>
       <c r="AO55" s="28"/>
       <c r="BA55" s="28">
@@ -21997,7 +22013,7 @@
       <c r="AL56">
         <v>8</v>
       </c>
-      <c r="AM56" s="128"/>
+      <c r="AM56" s="131"/>
       <c r="AN56" s="28"/>
       <c r="AO56" s="28">
         <v>30</v>
@@ -22021,7 +22037,7 @@
       <c r="AL57">
         <v>8</v>
       </c>
-      <c r="AM57" s="128"/>
+      <c r="AM57" s="131"/>
       <c r="AN57" s="28"/>
       <c r="AO57" s="28">
         <v>31</v>
@@ -22051,7 +22067,7 @@
       <c r="AL58">
         <v>8</v>
       </c>
-      <c r="AM58" s="128">
+      <c r="AM58" s="131">
         <v>2002</v>
       </c>
       <c r="AN58" s="28"/>
@@ -22080,7 +22096,7 @@
       <c r="AL59">
         <v>8</v>
       </c>
-      <c r="AM59" s="128"/>
+      <c r="AM59" s="131"/>
       <c r="AN59" s="28"/>
       <c r="AO59" s="28">
         <v>33</v>
@@ -22129,7 +22145,7 @@
       <c r="AL60">
         <v>10</v>
       </c>
-      <c r="AM60" s="128"/>
+      <c r="AM60" s="131"/>
       <c r="AN60" s="28"/>
       <c r="AO60" s="28">
         <v>34</v>
@@ -22168,7 +22184,7 @@
       <c r="AL61">
         <v>10</v>
       </c>
-      <c r="AM61" s="128"/>
+      <c r="AM61" s="131"/>
       <c r="AN61" s="28"/>
       <c r="AO61" s="28">
         <v>35</v>
@@ -22209,7 +22225,7 @@
       <c r="AL62">
         <v>10</v>
       </c>
-      <c r="AM62" s="128"/>
+      <c r="AM62" s="131"/>
       <c r="AN62" s="28"/>
       <c r="AO62" s="28">
         <v>36</v>
@@ -22248,7 +22264,7 @@
       <c r="AL63">
         <v>9</v>
       </c>
-      <c r="AM63" s="128">
+      <c r="AM63" s="131">
         <v>2003</v>
       </c>
       <c r="AN63" s="28"/>
@@ -22277,7 +22293,7 @@
       <c r="AL64">
         <v>11</v>
       </c>
-      <c r="AM64" s="128"/>
+      <c r="AM64" s="131"/>
       <c r="AN64" s="28"/>
       <c r="AO64" s="28">
         <v>37</v>
@@ -22310,7 +22326,7 @@
       <c r="AL65">
         <v>9</v>
       </c>
-      <c r="AM65" s="128"/>
+      <c r="AM65" s="131"/>
       <c r="AN65" s="28"/>
       <c r="AO65" s="28"/>
       <c r="BA65" s="28">
@@ -22362,7 +22378,7 @@
       <c r="AL66">
         <v>11</v>
       </c>
-      <c r="AM66" s="128"/>
+      <c r="AM66" s="131"/>
       <c r="AN66" s="28"/>
       <c r="AO66" s="28">
         <v>38</v>
@@ -22404,7 +22420,7 @@
       <c r="AL67">
         <v>9</v>
       </c>
-      <c r="AM67" s="128"/>
+      <c r="AM67" s="131"/>
       <c r="AN67" s="28"/>
       <c r="AO67" s="28"/>
       <c r="BA67" s="28">
@@ -22442,7 +22458,7 @@
       <c r="AL68">
         <v>11</v>
       </c>
-      <c r="AM68" s="128"/>
+      <c r="AM68" s="131"/>
       <c r="AN68" s="28"/>
       <c r="AO68" s="28">
         <v>39</v>
@@ -22481,7 +22497,7 @@
       <c r="AL69">
         <v>9</v>
       </c>
-      <c r="AM69" s="128">
+      <c r="AM69" s="131">
         <v>2004</v>
       </c>
       <c r="AN69" s="28"/>
@@ -22510,7 +22526,7 @@
       <c r="AL70">
         <v>10</v>
       </c>
-      <c r="AM70" s="128"/>
+      <c r="AM70" s="131"/>
       <c r="AN70" s="28"/>
       <c r="AO70" s="28">
         <v>40</v>
@@ -22546,7 +22562,7 @@
       <c r="AL71">
         <v>10</v>
       </c>
-      <c r="AM71" s="128"/>
+      <c r="AM71" s="131"/>
       <c r="AN71" s="28"/>
       <c r="AO71" s="28">
         <v>41</v>
@@ -22606,7 +22622,7 @@
       <c r="AL72">
         <v>10</v>
       </c>
-      <c r="AM72" s="128"/>
+      <c r="AM72" s="131"/>
       <c r="AN72" s="28"/>
       <c r="AO72" s="28">
         <v>42</v>
@@ -22648,7 +22664,7 @@
       <c r="AL73">
         <v>10</v>
       </c>
-      <c r="AM73" s="128"/>
+      <c r="AM73" s="131"/>
       <c r="AN73" s="28"/>
       <c r="AO73" s="28">
         <v>43</v>
@@ -22669,19 +22685,19 @@
       <c r="BK73" s="28"/>
     </row>
     <row r="74" spans="12:63" x14ac:dyDescent="0.4">
-      <c r="N74" s="130" t="s">
+      <c r="N74" s="133" t="s">
         <v>446</v>
       </c>
-      <c r="O74" s="130" t="s">
+      <c r="O74" s="133" t="s">
         <v>375</v>
       </c>
       <c r="P74" s="34" t="s">
         <v>376</v>
       </c>
-      <c r="Q74" s="130" t="s">
+      <c r="Q74" s="133" t="s">
         <v>377</v>
       </c>
-      <c r="R74" s="130" t="s">
+      <c r="R74" s="133" t="s">
         <v>377</v>
       </c>
       <c r="AJ74">
@@ -22716,10 +22732,10 @@
       <c r="BK74" s="28"/>
     </row>
     <row r="75" spans="12:63" x14ac:dyDescent="0.4">
-      <c r="N75" s="130"/>
-      <c r="O75" s="130"/>
-      <c r="Q75" s="130"/>
-      <c r="R75" s="130"/>
+      <c r="N75" s="133"/>
+      <c r="O75" s="133"/>
+      <c r="Q75" s="133"/>
+      <c r="R75" s="133"/>
       <c r="AJ75">
         <v>70</v>
       </c>
@@ -22801,7 +22817,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1A7CFB-21FB-4063-A8BA-DA63D8E3A67D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:N52"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
@@ -23215,12 +23231,12 @@
       <c r="C42" t="s">
         <v>464</v>
       </c>
-      <c r="D42" s="109" t="s">
+      <c r="D42" s="107" t="s">
         <v>647</v>
       </c>
       <c r="E42" s="31"/>
-      <c r="F42" s="109"/>
-      <c r="G42" s="109" t="s">
+      <c r="F42" s="107"/>
+      <c r="G42" s="107" t="s">
         <v>649</v>
       </c>
     </row>
@@ -23228,12 +23244,12 @@
       <c r="C43" t="s">
         <v>465</v>
       </c>
-      <c r="D43" s="109" t="s">
+      <c r="D43" s="107" t="s">
         <v>649</v>
       </c>
       <c r="E43" s="31"/>
-      <c r="F43" s="109"/>
-      <c r="G43" s="109" t="s">
+      <c r="F43" s="107"/>
+      <c r="G43" s="107" t="s">
         <v>645</v>
       </c>
     </row>
@@ -23241,15 +23257,15 @@
       <c r="C44" t="s">
         <v>349</v>
       </c>
-      <c r="D44" s="109" t="s">
+      <c r="D44" s="107" t="s">
         <v>647</v>
       </c>
       <c r="E44" s="31"/>
       <c r="F44" s="31"/>
-      <c r="G44" s="109" t="s">
+      <c r="G44" s="107" t="s">
         <v>648</v>
       </c>
-      <c r="H44" s="109" t="s">
+      <c r="H44" s="107" t="s">
         <v>646</v>
       </c>
     </row>
@@ -23257,12 +23273,12 @@
       <c r="C45" t="s">
         <v>350</v>
       </c>
-      <c r="D45" s="109" t="s">
+      <c r="D45" s="107" t="s">
         <v>647</v>
       </c>
       <c r="E45" s="31"/>
-      <c r="F45" s="109"/>
-      <c r="G45" s="109" t="s">
+      <c r="F45" s="107"/>
+      <c r="G45" s="107" t="s">
         <v>649</v>
       </c>
     </row>
@@ -23270,73 +23286,73 @@
       <c r="C46" t="s">
         <v>348</v>
       </c>
-      <c r="D46" s="109" t="s">
+      <c r="D46" s="107" t="s">
         <v>649</v>
       </c>
       <c r="E46" s="31"/>
-      <c r="F46" s="109"/>
-      <c r="G46" s="109" t="s">
+      <c r="F46" s="107"/>
+      <c r="G46" s="107" t="s">
         <v>645</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.4">
       <c r="E47" s="31"/>
-      <c r="F47" s="109"/>
+      <c r="F47" s="107"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.4">
       <c r="C48" t="s">
         <v>650</v>
       </c>
-      <c r="D48" s="109" t="s">
+      <c r="D48" s="107" t="s">
         <v>651</v>
       </c>
       <c r="E48" s="31" t="s">
         <v>654</v>
       </c>
-      <c r="F48" s="109" t="s">
+      <c r="F48" s="107" t="s">
         <v>654</v>
       </c>
-      <c r="G48" s="109" t="s">
+      <c r="G48" s="107" t="s">
         <v>679</v>
       </c>
     </row>
     <row r="49" spans="3:8" x14ac:dyDescent="0.4">
-      <c r="D49" s="109"/>
-      <c r="F49" s="109"/>
-      <c r="G49" s="109" t="s">
+      <c r="D49" s="107"/>
+      <c r="F49" s="107"/>
+      <c r="G49" s="107" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="50" spans="3:8" x14ac:dyDescent="0.4">
-      <c r="D50" s="109"/>
-      <c r="E50" s="109"/>
-      <c r="F50" s="109"/>
-      <c r="G50" s="109"/>
+      <c r="D50" s="107"/>
+      <c r="E50" s="107"/>
+      <c r="F50" s="107"/>
+      <c r="G50" s="107"/>
     </row>
     <row r="51" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C51" t="s">
         <v>653</v>
       </c>
-      <c r="D51" s="109" t="s">
+      <c r="D51" s="107" t="s">
         <v>677</v>
       </c>
-      <c r="E51" s="109" t="s">
+      <c r="E51" s="107" t="s">
         <v>676</v>
       </c>
-      <c r="F51" s="109" t="s">
+      <c r="F51" s="107" t="s">
         <v>676</v>
       </c>
-      <c r="G51" s="109" t="s">
+      <c r="G51" s="107" t="s">
         <v>678</v>
       </c>
     </row>
     <row r="52" spans="3:8" x14ac:dyDescent="0.4">
-      <c r="D52" s="120" t="s">
+      <c r="D52" s="118" t="s">
         <v>681</v>
       </c>
-      <c r="E52" s="109"/>
-      <c r="F52" s="109"/>
-      <c r="G52" s="109" t="s">
+      <c r="E52" s="107"/>
+      <c r="F52" s="107"/>
+      <c r="G52" s="107" t="s">
         <v>680</v>
       </c>
       <c r="H52">
@@ -23350,7 +23366,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71F45865-C074-4AAC-A678-7239DCA4178F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:P30"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -23474,7 +23490,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54004B24-A008-4266-8735-D57DCB8AD55A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData/>
